--- a/internal_doc/05.测试设计/story/mysql连接器/5.7.24测试用例差别.xlsx
+++ b/internal_doc/05.测试设计/story/mysql连接器/5.7.24测试用例差别.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="557" uniqueCount="251">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="569" uniqueCount="251">
   <si>
     <t>r</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -1245,17 +1245,16 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <sheetPr filterMode="1"/>
   <dimension ref="A1:D180"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="1" width="28" customWidth="1"/>
+    <col min="1" max="1" width="34.5" customWidth="1"/>
     <col min="2" max="2" width="25.375" customWidth="1"/>
     <col min="3" max="3" width="76.375" customWidth="1"/>
     <col min="4" max="4" width="43.375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="20.100000000000001" customHeight="1">
+    <row r="1" spans="1:4" ht="30" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>28</v>
       </c>
@@ -1269,15 +1268,17 @@
         <v>224</v>
       </c>
     </row>
-    <row r="2" spans="1:4" hidden="1">
-      <c r="A2" t="s">
+    <row r="2" spans="1:4" ht="30" customHeight="1">
+      <c r="A2" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" s="1" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="3" spans="1:4" ht="20.100000000000001" customHeight="1">
+      <c r="C2" s="1"/>
+      <c r="D2" s="1"/>
+    </row>
+    <row r="3" spans="1:4" ht="30" customHeight="1">
       <c r="A3" s="1" t="s">
         <v>160</v>
       </c>
@@ -1291,15 +1292,17 @@
         <v>225</v>
       </c>
     </row>
-    <row r="4" spans="1:4" hidden="1">
-      <c r="A4" t="s">
+    <row r="4" spans="1:4" ht="30" customHeight="1">
+      <c r="A4" s="1" t="s">
         <v>161</v>
       </c>
-      <c r="B4" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" ht="20.100000000000001" customHeight="1">
+      <c r="B4" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C4" s="1"/>
+      <c r="D4" s="1"/>
+    </row>
+    <row r="5" spans="1:4" ht="30" customHeight="1">
       <c r="A5" s="1" t="s">
         <v>31</v>
       </c>
@@ -1313,23 +1316,27 @@
         <v>225</v>
       </c>
     </row>
-    <row r="6" spans="1:4" hidden="1">
-      <c r="A6" t="s">
+    <row r="6" spans="1:4" ht="30" customHeight="1">
+      <c r="A6" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="B6" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" hidden="1">
-      <c r="A7" t="s">
+      <c r="B6" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C6" s="1"/>
+      <c r="D6" s="1"/>
+    </row>
+    <row r="7" spans="1:4" ht="30" customHeight="1">
+      <c r="A7" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="B7" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" ht="20.100000000000001" customHeight="1">
+      <c r="B7" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C7" s="1"/>
+      <c r="D7" s="1"/>
+    </row>
+    <row r="8" spans="1:4" ht="30" customHeight="1">
       <c r="A8" s="1" t="s">
         <v>162</v>
       </c>
@@ -1343,31 +1350,37 @@
         <v>225</v>
       </c>
     </row>
-    <row r="9" spans="1:4" hidden="1">
-      <c r="A9" t="s">
+    <row r="9" spans="1:4" ht="30" customHeight="1">
+      <c r="A9" s="1" t="s">
         <v>163</v>
       </c>
-      <c r="B9" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" hidden="1">
-      <c r="A10" t="s">
+      <c r="B9" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C9" s="1"/>
+      <c r="D9" s="1"/>
+    </row>
+    <row r="10" spans="1:4" ht="30" customHeight="1">
+      <c r="A10" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="B10" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" hidden="1">
-      <c r="A11" t="s">
+      <c r="B10" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C10" s="1"/>
+      <c r="D10" s="1"/>
+    </row>
+    <row r="11" spans="1:4" ht="30" customHeight="1">
+      <c r="A11" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="B11" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" ht="20.100000000000001" customHeight="1">
+      <c r="B11" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C11" s="1"/>
+      <c r="D11" s="1"/>
+    </row>
+    <row r="12" spans="1:4" ht="30" customHeight="1">
       <c r="A12" s="1" t="s">
         <v>36</v>
       </c>
@@ -1381,7 +1394,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="13" spans="1:4" ht="20.100000000000001" customHeight="1">
+    <row r="13" spans="1:4" ht="30" customHeight="1">
       <c r="A13" s="1" t="s">
         <v>37</v>
       </c>
@@ -1395,23 +1408,27 @@
         <v>225</v>
       </c>
     </row>
-    <row r="14" spans="1:4" hidden="1">
-      <c r="A14" t="s">
+    <row r="14" spans="1:4" ht="30" customHeight="1">
+      <c r="A14" s="1" t="s">
         <v>164</v>
       </c>
-      <c r="B14" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4" hidden="1">
-      <c r="A15" t="s">
+      <c r="B14" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C14" s="1"/>
+      <c r="D14" s="1"/>
+    </row>
+    <row r="15" spans="1:4" ht="30" customHeight="1">
+      <c r="A15" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="B15" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4" ht="20.100000000000001" customHeight="1">
+      <c r="B15" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C15" s="1"/>
+      <c r="D15" s="1"/>
+    </row>
+    <row r="16" spans="1:4" ht="30" customHeight="1">
       <c r="A16" s="1" t="s">
         <v>39</v>
       </c>
@@ -1425,47 +1442,57 @@
         <v>225</v>
       </c>
     </row>
-    <row r="17" spans="1:4" hidden="1">
-      <c r="A17" t="s">
+    <row r="17" spans="1:4" ht="30" customHeight="1">
+      <c r="A17" s="1" t="s">
         <v>165</v>
       </c>
-      <c r="B17" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4" hidden="1">
-      <c r="A18" t="s">
+      <c r="B17" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C17" s="1"/>
+      <c r="D17" s="1"/>
+    </row>
+    <row r="18" spans="1:4" ht="30" customHeight="1">
+      <c r="A18" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="B18" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4" hidden="1">
-      <c r="A19" t="s">
+      <c r="B18" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C18" s="1"/>
+      <c r="D18" s="1"/>
+    </row>
+    <row r="19" spans="1:4" ht="30" customHeight="1">
+      <c r="A19" s="1" t="s">
         <v>166</v>
       </c>
-      <c r="B19" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="20" spans="1:4" hidden="1">
-      <c r="A20" t="s">
+      <c r="B19" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C19" s="1"/>
+      <c r="D19" s="1"/>
+    </row>
+    <row r="20" spans="1:4" ht="30" customHeight="1">
+      <c r="A20" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="B20" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="21" spans="1:4" hidden="1">
-      <c r="A21" t="s">
+      <c r="B20" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C20" s="1"/>
+      <c r="D20" s="1"/>
+    </row>
+    <row r="21" spans="1:4" ht="30" customHeight="1">
+      <c r="A21" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="B21" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="22" spans="1:4" ht="20.100000000000001" customHeight="1">
+      <c r="B21" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C21" s="1"/>
+      <c r="D21" s="1"/>
+    </row>
+    <row r="22" spans="1:4" ht="30" customHeight="1">
       <c r="A22" s="1" t="s">
         <v>43</v>
       </c>
@@ -1479,7 +1506,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="23" spans="1:4" ht="20.100000000000001" customHeight="1">
+    <row r="23" spans="1:4" ht="30" customHeight="1">
       <c r="A23" s="1" t="s">
         <v>44</v>
       </c>
@@ -1493,7 +1520,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="24" spans="1:4" ht="20.100000000000001" customHeight="1">
+    <row r="24" spans="1:4" ht="30" customHeight="1">
       <c r="A24" s="1" t="s">
         <v>227</v>
       </c>
@@ -1507,7 +1534,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="25" spans="1:4" ht="20.100000000000001" customHeight="1">
+    <row r="25" spans="1:4" ht="30" customHeight="1">
       <c r="A25" s="1" t="s">
         <v>45</v>
       </c>
@@ -1521,7 +1548,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="26" spans="1:4" ht="20.100000000000001" customHeight="1">
+    <row r="26" spans="1:4" ht="30" customHeight="1">
       <c r="A26" s="1" t="s">
         <v>46</v>
       </c>
@@ -1535,7 +1562,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="27" spans="1:4" ht="20.100000000000001" customHeight="1">
+    <row r="27" spans="1:4" ht="30" customHeight="1">
       <c r="A27" s="1" t="s">
         <v>47</v>
       </c>
@@ -1549,7 +1576,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="28" spans="1:4" ht="20.100000000000001" customHeight="1">
+    <row r="28" spans="1:4" ht="30" customHeight="1">
       <c r="A28" s="1" t="s">
         <v>48</v>
       </c>
@@ -1563,7 +1590,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="29" spans="1:4" ht="20.100000000000001" customHeight="1">
+    <row r="29" spans="1:4" ht="30" customHeight="1">
       <c r="A29" s="1" t="s">
         <v>49</v>
       </c>
@@ -1577,7 +1604,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="30" spans="1:4" ht="20.100000000000001" customHeight="1">
+    <row r="30" spans="1:4" ht="30" customHeight="1">
       <c r="A30" s="1" t="s">
         <v>50</v>
       </c>
@@ -1591,7 +1618,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="31" spans="1:4" ht="20.100000000000001" customHeight="1">
+    <row r="31" spans="1:4" ht="30" customHeight="1">
       <c r="A31" s="1" t="s">
         <v>167</v>
       </c>
@@ -1605,79 +1632,97 @@
         <v>225</v>
       </c>
     </row>
-    <row r="32" spans="1:4" hidden="1">
-      <c r="A32" t="s">
+    <row r="32" spans="1:4" ht="30" customHeight="1">
+      <c r="A32" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="B32" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="33" spans="1:4" hidden="1">
-      <c r="A33" t="s">
+      <c r="B32" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C32" s="1"/>
+      <c r="D32" s="1"/>
+    </row>
+    <row r="33" spans="1:4" ht="30" customHeight="1">
+      <c r="A33" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="B33" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="34" spans="1:4" hidden="1">
-      <c r="A34" t="s">
+      <c r="B33" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C33" s="1"/>
+      <c r="D33" s="1"/>
+    </row>
+    <row r="34" spans="1:4" ht="30" customHeight="1">
+      <c r="A34" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="B34" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="35" spans="1:4" hidden="1">
-      <c r="A35" t="s">
+      <c r="B34" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C34" s="1"/>
+      <c r="D34" s="1"/>
+    </row>
+    <row r="35" spans="1:4" ht="30" customHeight="1">
+      <c r="A35" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="B35" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="36" spans="1:4" hidden="1">
-      <c r="A36" t="s">
+      <c r="B35" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C35" s="1"/>
+      <c r="D35" s="1"/>
+    </row>
+    <row r="36" spans="1:4" ht="30" customHeight="1">
+      <c r="A36" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="B36" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="37" spans="1:4" hidden="1">
-      <c r="A37" t="s">
+      <c r="B36" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C36" s="1"/>
+      <c r="D36" s="1"/>
+    </row>
+    <row r="37" spans="1:4" ht="30" customHeight="1">
+      <c r="A37" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="B37" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="38" spans="1:4" hidden="1">
-      <c r="A38" t="s">
+      <c r="B37" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C37" s="1"/>
+      <c r="D37" s="1"/>
+    </row>
+    <row r="38" spans="1:4" ht="30" customHeight="1">
+      <c r="A38" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="B38" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="39" spans="1:4" hidden="1">
-      <c r="A39" t="s">
+      <c r="B38" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C38" s="1"/>
+      <c r="D38" s="1"/>
+    </row>
+    <row r="39" spans="1:4" ht="30" customHeight="1">
+      <c r="A39" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="B39" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="40" spans="1:4" hidden="1">
-      <c r="A40" t="s">
+      <c r="B39" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C39" s="1"/>
+      <c r="D39" s="1"/>
+    </row>
+    <row r="40" spans="1:4" ht="30" customHeight="1">
+      <c r="A40" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="B40" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="41" spans="1:4" ht="20.100000000000001" customHeight="1">
+      <c r="B40" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C40" s="1"/>
+      <c r="D40" s="1"/>
+    </row>
+    <row r="41" spans="1:4" ht="30" customHeight="1">
       <c r="A41" s="1" t="s">
         <v>60</v>
       </c>
@@ -1691,7 +1736,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="42" spans="1:4" ht="20.100000000000001" customHeight="1">
+    <row r="42" spans="1:4" ht="30" customHeight="1">
       <c r="A42" s="1" t="s">
         <v>61</v>
       </c>
@@ -1705,7 +1750,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="43" spans="1:4" ht="20.100000000000001" customHeight="1">
+    <row r="43" spans="1:4" ht="30" customHeight="1">
       <c r="A43" s="1" t="s">
         <v>62</v>
       </c>
@@ -1719,175 +1764,217 @@
         <v>225</v>
       </c>
     </row>
-    <row r="44" spans="1:4" hidden="1">
-      <c r="A44" t="s">
+    <row r="44" spans="1:4" ht="30" customHeight="1">
+      <c r="A44" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="B44" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="45" spans="1:4" hidden="1">
-      <c r="A45" t="s">
+      <c r="B44" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C44" s="1"/>
+      <c r="D44" s="1"/>
+    </row>
+    <row r="45" spans="1:4" ht="30" customHeight="1">
+      <c r="A45" s="1" t="s">
         <v>169</v>
       </c>
-      <c r="B45" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="46" spans="1:4" hidden="1">
-      <c r="A46" t="s">
+      <c r="B45" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C45" s="1"/>
+      <c r="D45" s="1"/>
+    </row>
+    <row r="46" spans="1:4" ht="30" customHeight="1">
+      <c r="A46" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="B46" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="47" spans="1:4" hidden="1">
-      <c r="A47" t="s">
+      <c r="B46" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C46" s="1"/>
+      <c r="D46" s="1"/>
+    </row>
+    <row r="47" spans="1:4" ht="30" customHeight="1">
+      <c r="A47" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="B47" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="48" spans="1:4" hidden="1">
-      <c r="A48" t="s">
+      <c r="B47" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C47" s="1"/>
+      <c r="D47" s="1"/>
+    </row>
+    <row r="48" spans="1:4" ht="30" customHeight="1">
+      <c r="A48" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="B48" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="49" spans="1:2" hidden="1">
-      <c r="A49" t="s">
+      <c r="B48" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C48" s="1"/>
+      <c r="D48" s="1"/>
+    </row>
+    <row r="49" spans="1:4" ht="30" customHeight="1">
+      <c r="A49" s="1" t="s">
         <v>170</v>
       </c>
-      <c r="B49" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="50" spans="1:2" hidden="1">
-      <c r="A50" t="s">
+      <c r="B49" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C49" s="1"/>
+      <c r="D49" s="1"/>
+    </row>
+    <row r="50" spans="1:4" ht="30" customHeight="1">
+      <c r="A50" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="B50" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="51" spans="1:2" hidden="1">
-      <c r="A51" t="s">
+      <c r="B50" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C50" s="1"/>
+      <c r="D50" s="1"/>
+    </row>
+    <row r="51" spans="1:4" ht="30" customHeight="1">
+      <c r="A51" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="B51" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="52" spans="1:2" hidden="1">
-      <c r="A52" t="s">
+      <c r="B51" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C51" s="1"/>
+      <c r="D51" s="1"/>
+    </row>
+    <row r="52" spans="1:4" ht="30" customHeight="1">
+      <c r="A52" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="B52" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="53" spans="1:2" hidden="1">
-      <c r="A53" t="s">
+      <c r="B52" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C52" s="1"/>
+      <c r="D52" s="1"/>
+    </row>
+    <row r="53" spans="1:4" ht="30" customHeight="1">
+      <c r="A53" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="B53" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="54" spans="1:2" hidden="1">
-      <c r="A54" t="s">
+      <c r="B53" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C53" s="1"/>
+      <c r="D53" s="1"/>
+    </row>
+    <row r="54" spans="1:4" ht="30" customHeight="1">
+      <c r="A54" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="B54" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="55" spans="1:2" hidden="1">
-      <c r="A55" t="s">
+      <c r="B54" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C54" s="1"/>
+      <c r="D54" s="1"/>
+    </row>
+    <row r="55" spans="1:4" ht="30" customHeight="1">
+      <c r="A55" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="B55" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="56" spans="1:2" hidden="1">
-      <c r="A56" t="s">
+      <c r="B55" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C55" s="1"/>
+      <c r="D55" s="1"/>
+    </row>
+    <row r="56" spans="1:4" ht="30" customHeight="1">
+      <c r="A56" s="1" t="s">
         <v>171</v>
       </c>
-      <c r="B56" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="57" spans="1:2" hidden="1">
-      <c r="A57" t="s">
+      <c r="B56" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C56" s="1"/>
+      <c r="D56" s="1"/>
+    </row>
+    <row r="57" spans="1:4" ht="30" customHeight="1">
+      <c r="A57" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="B57" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="58" spans="1:2" hidden="1">
-      <c r="A58" t="s">
+      <c r="B57" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C57" s="1"/>
+      <c r="D57" s="1"/>
+    </row>
+    <row r="58" spans="1:4" ht="30" customHeight="1">
+      <c r="A58" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="B58" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="59" spans="1:2" hidden="1">
-      <c r="A59" t="s">
+      <c r="B58" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C58" s="1"/>
+      <c r="D58" s="1"/>
+    </row>
+    <row r="59" spans="1:4" ht="30" customHeight="1">
+      <c r="A59" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="B59" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="60" spans="1:2" hidden="1">
-      <c r="A60" t="s">
+      <c r="B59" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C59" s="1"/>
+      <c r="D59" s="1"/>
+    </row>
+    <row r="60" spans="1:4" ht="30" customHeight="1">
+      <c r="A60" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="B60" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="61" spans="1:2" hidden="1">
-      <c r="A61" t="s">
+      <c r="B60" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C60" s="1"/>
+      <c r="D60" s="1"/>
+    </row>
+    <row r="61" spans="1:4" ht="30" customHeight="1">
+      <c r="A61" s="1" t="s">
         <v>76</v>
       </c>
-      <c r="B61" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="62" spans="1:2" hidden="1">
-      <c r="A62" t="s">
+      <c r="B61" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C61" s="1"/>
+      <c r="D61" s="1"/>
+    </row>
+    <row r="62" spans="1:4" ht="30" customHeight="1">
+      <c r="A62" s="1" t="s">
         <v>77</v>
       </c>
-      <c r="B62" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="63" spans="1:2" hidden="1">
-      <c r="A63" t="s">
+      <c r="B62" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C62" s="1"/>
+      <c r="D62" s="1"/>
+    </row>
+    <row r="63" spans="1:4" ht="30" customHeight="1">
+      <c r="A63" s="1" t="s">
         <v>172</v>
       </c>
-      <c r="B63" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="64" spans="1:2" hidden="1">
-      <c r="A64" t="s">
+      <c r="B63" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C63" s="1"/>
+      <c r="D63" s="1"/>
+    </row>
+    <row r="64" spans="1:4" ht="30" customHeight="1">
+      <c r="A64" s="1" t="s">
         <v>173</v>
       </c>
-      <c r="B64" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="65" spans="1:4" ht="20.100000000000001" customHeight="1">
+      <c r="B64" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C64" s="1"/>
+      <c r="D64" s="1"/>
+    </row>
+    <row r="65" spans="1:4" ht="30" customHeight="1">
       <c r="A65" s="1" t="s">
         <v>174</v>
       </c>
@@ -1901,7 +1988,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="66" spans="1:4" ht="20.100000000000001" customHeight="1">
+    <row r="66" spans="1:4" ht="30" customHeight="1">
       <c r="A66" s="1" t="s">
         <v>78</v>
       </c>
@@ -1915,7 +2002,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="67" spans="1:4" ht="20.100000000000001" customHeight="1">
+    <row r="67" spans="1:4" ht="30" customHeight="1">
       <c r="A67" s="1" t="s">
         <v>79</v>
       </c>
@@ -1929,7 +2016,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="68" spans="1:4" ht="20.100000000000001" customHeight="1">
+    <row r="68" spans="1:4" ht="30" customHeight="1">
       <c r="A68" s="1" t="s">
         <v>175</v>
       </c>
@@ -1943,87 +2030,107 @@
         <v>228</v>
       </c>
     </row>
-    <row r="69" spans="1:4" hidden="1">
-      <c r="A69" t="s">
+    <row r="69" spans="1:4" ht="30" customHeight="1">
+      <c r="A69" s="1" t="s">
         <v>176</v>
       </c>
-      <c r="B69" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="70" spans="1:4" hidden="1">
-      <c r="A70" t="s">
+      <c r="B69" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C69" s="1"/>
+      <c r="D69" s="1"/>
+    </row>
+    <row r="70" spans="1:4" ht="30" customHeight="1">
+      <c r="A70" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="B70" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="71" spans="1:4" hidden="1">
-      <c r="A71" t="s">
+      <c r="B70" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C70" s="1"/>
+      <c r="D70" s="1"/>
+    </row>
+    <row r="71" spans="1:4" ht="30" customHeight="1">
+      <c r="A71" s="1" t="s">
         <v>203</v>
       </c>
-      <c r="B71" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="72" spans="1:4" hidden="1">
-      <c r="A72" t="s">
+      <c r="B71" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C71" s="1"/>
+      <c r="D71" s="1"/>
+    </row>
+    <row r="72" spans="1:4" ht="30" customHeight="1">
+      <c r="A72" s="1" t="s">
         <v>204</v>
       </c>
-      <c r="B72" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="73" spans="1:4" hidden="1">
-      <c r="A73" t="s">
+      <c r="B72" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C72" s="1"/>
+      <c r="D72" s="1"/>
+    </row>
+    <row r="73" spans="1:4" ht="30" customHeight="1">
+      <c r="A73" s="1" t="s">
         <v>207</v>
       </c>
-      <c r="B73" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="74" spans="1:4" hidden="1">
-      <c r="A74" t="s">
+      <c r="B73" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C73" s="1"/>
+      <c r="D73" s="1"/>
+    </row>
+    <row r="74" spans="1:4" ht="30" customHeight="1">
+      <c r="A74" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="B74" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="75" spans="1:4" hidden="1">
-      <c r="A75" t="s">
+      <c r="B74" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C74" s="1"/>
+      <c r="D74" s="1"/>
+    </row>
+    <row r="75" spans="1:4" ht="30" customHeight="1">
+      <c r="A75" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="B75" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="76" spans="1:4" hidden="1">
-      <c r="A76" t="s">
+      <c r="B75" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C75" s="1"/>
+      <c r="D75" s="1"/>
+    </row>
+    <row r="76" spans="1:4" ht="30" customHeight="1">
+      <c r="A76" s="1" t="s">
         <v>206</v>
       </c>
-      <c r="B76" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="77" spans="1:4" hidden="1">
-      <c r="A77" t="s">
+      <c r="B76" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C76" s="1"/>
+      <c r="D76" s="1"/>
+    </row>
+    <row r="77" spans="1:4" ht="30" customHeight="1">
+      <c r="A77" s="1" t="s">
         <v>205</v>
       </c>
-      <c r="B77" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="78" spans="1:4" hidden="1">
-      <c r="A78" t="s">
+      <c r="B77" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C77" s="1"/>
+      <c r="D77" s="1"/>
+    </row>
+    <row r="78" spans="1:4" ht="30" customHeight="1">
+      <c r="A78" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="B78" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="79" spans="1:4" ht="20.100000000000001" customHeight="1">
+      <c r="B78" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C78" s="1"/>
+      <c r="D78" s="1"/>
+    </row>
+    <row r="79" spans="1:4" ht="30" customHeight="1">
       <c r="A79" s="1" t="s">
         <v>84</v>
       </c>
@@ -2037,135 +2144,167 @@
         <v>225</v>
       </c>
     </row>
-    <row r="80" spans="1:4" hidden="1">
-      <c r="A80" t="s">
+    <row r="80" spans="1:4" ht="30" customHeight="1">
+      <c r="A80" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="B80" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="81" spans="1:4" hidden="1">
-      <c r="A81" t="s">
+      <c r="B80" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C80" s="1"/>
+      <c r="D80" s="1"/>
+    </row>
+    <row r="81" spans="1:4" ht="30" customHeight="1">
+      <c r="A81" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="B81" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="82" spans="1:4" hidden="1">
-      <c r="A82" t="s">
+      <c r="B81" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C81" s="1"/>
+      <c r="D81" s="1"/>
+    </row>
+    <row r="82" spans="1:4" ht="30" customHeight="1">
+      <c r="A82" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="B82" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="83" spans="1:4" hidden="1">
-      <c r="A83" t="s">
+      <c r="B82" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C82" s="1"/>
+      <c r="D82" s="1"/>
+    </row>
+    <row r="83" spans="1:4" ht="30" customHeight="1">
+      <c r="A83" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="B83" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="84" spans="1:4" hidden="1">
-      <c r="A84" t="s">
+      <c r="B83" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C83" s="1"/>
+      <c r="D83" s="1"/>
+    </row>
+    <row r="84" spans="1:4" ht="30" customHeight="1">
+      <c r="A84" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="B84" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="85" spans="1:4" hidden="1">
-      <c r="A85" t="s">
+      <c r="B84" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C84" s="1"/>
+      <c r="D84" s="1"/>
+    </row>
+    <row r="85" spans="1:4" ht="30" customHeight="1">
+      <c r="A85" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="B85" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="86" spans="1:4" hidden="1">
-      <c r="A86" t="s">
+      <c r="B85" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C85" s="1"/>
+      <c r="D85" s="1"/>
+    </row>
+    <row r="86" spans="1:4" ht="30" customHeight="1">
+      <c r="A86" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="B86" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="87" spans="1:4" hidden="1">
-      <c r="A87" t="s">
+      <c r="B86" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C86" s="1"/>
+      <c r="D86" s="1"/>
+    </row>
+    <row r="87" spans="1:4" ht="30" customHeight="1">
+      <c r="A87" s="1" t="s">
         <v>92</v>
       </c>
-      <c r="B87" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="88" spans="1:4" hidden="1">
-      <c r="A88" t="s">
+      <c r="B87" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C87" s="1"/>
+      <c r="D87" s="1"/>
+    </row>
+    <row r="88" spans="1:4" ht="30" customHeight="1">
+      <c r="A88" s="1" t="s">
         <v>93</v>
       </c>
-      <c r="B88" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="89" spans="1:4" hidden="1">
-      <c r="A89" t="s">
+      <c r="B88" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C88" s="1"/>
+      <c r="D88" s="1"/>
+    </row>
+    <row r="89" spans="1:4" ht="30" customHeight="1">
+      <c r="A89" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="B89" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="90" spans="1:4" hidden="1">
-      <c r="A90" t="s">
+      <c r="B89" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C89" s="1"/>
+      <c r="D89" s="1"/>
+    </row>
+    <row r="90" spans="1:4" ht="30" customHeight="1">
+      <c r="A90" s="1" t="s">
         <v>95</v>
       </c>
-      <c r="B90" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="91" spans="1:4" hidden="1">
-      <c r="A91" t="s">
+      <c r="B90" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C90" s="1"/>
+      <c r="D90" s="1"/>
+    </row>
+    <row r="91" spans="1:4" ht="30" customHeight="1">
+      <c r="A91" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="B91" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="92" spans="1:4" hidden="1">
-      <c r="A92" t="s">
+      <c r="B91" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C91" s="1"/>
+      <c r="D91" s="1"/>
+    </row>
+    <row r="92" spans="1:4" ht="30" customHeight="1">
+      <c r="A92" s="1" t="s">
         <v>97</v>
       </c>
-      <c r="B92" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="93" spans="1:4" hidden="1">
-      <c r="A93" t="s">
+      <c r="B92" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C92" s="1"/>
+      <c r="D92" s="1"/>
+    </row>
+    <row r="93" spans="1:4" ht="30" customHeight="1">
+      <c r="A93" s="1" t="s">
         <v>98</v>
       </c>
-      <c r="B93" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="94" spans="1:4" hidden="1">
-      <c r="A94" t="s">
+      <c r="B93" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C93" s="1"/>
+      <c r="D93" s="1"/>
+    </row>
+    <row r="94" spans="1:4" ht="30" customHeight="1">
+      <c r="A94" s="1" t="s">
         <v>99</v>
       </c>
-      <c r="B94" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="95" spans="1:4" hidden="1">
-      <c r="A95" t="s">
+      <c r="B94" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C94" s="1"/>
+      <c r="D94" s="1"/>
+    </row>
+    <row r="95" spans="1:4" ht="30" customHeight="1">
+      <c r="A95" s="1" t="s">
         <v>201</v>
       </c>
-      <c r="B95" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="96" spans="1:4" ht="20.100000000000001" customHeight="1">
+      <c r="B95" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C95" s="1"/>
+      <c r="D95" s="1"/>
+    </row>
+    <row r="96" spans="1:4" ht="30" customHeight="1">
       <c r="A96" s="1" t="s">
         <v>100</v>
       </c>
@@ -2179,15 +2318,17 @@
         <v>225</v>
       </c>
     </row>
-    <row r="97" spans="1:4" hidden="1">
-      <c r="A97" t="s">
+    <row r="97" spans="1:4" ht="30" customHeight="1">
+      <c r="A97" s="1" t="s">
         <v>202</v>
       </c>
-      <c r="B97" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="98" spans="1:4" ht="20.100000000000001" customHeight="1">
+      <c r="B97" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C97" s="1"/>
+      <c r="D97" s="1"/>
+    </row>
+    <row r="98" spans="1:4" ht="30" customHeight="1">
       <c r="A98" s="1" t="s">
         <v>200</v>
       </c>
@@ -2201,247 +2342,307 @@
         <v>225</v>
       </c>
     </row>
-    <row r="99" spans="1:4" hidden="1">
-      <c r="A99" t="s">
+    <row r="99" spans="1:4" ht="30" customHeight="1">
+      <c r="A99" s="1" t="s">
         <v>101</v>
       </c>
-      <c r="B99" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="100" spans="1:4" hidden="1">
-      <c r="A100" t="s">
+      <c r="B99" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C99" s="1"/>
+      <c r="D99" s="1"/>
+    </row>
+    <row r="100" spans="1:4" ht="30" customHeight="1">
+      <c r="A100" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="B100" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="101" spans="1:4" hidden="1">
-      <c r="A101" t="s">
+      <c r="B100" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C100" s="1"/>
+      <c r="D100" s="1"/>
+    </row>
+    <row r="101" spans="1:4" ht="30" customHeight="1">
+      <c r="A101" s="1" t="s">
         <v>103</v>
       </c>
-      <c r="B101" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="102" spans="1:4" hidden="1">
-      <c r="A102" t="s">
+      <c r="B101" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C101" s="1"/>
+      <c r="D101" s="1"/>
+    </row>
+    <row r="102" spans="1:4" ht="30" customHeight="1">
+      <c r="A102" s="1" t="s">
         <v>104</v>
       </c>
-      <c r="B102" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="103" spans="1:4" hidden="1">
-      <c r="A103" t="s">
+      <c r="B102" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C102" s="1"/>
+      <c r="D102" s="1"/>
+    </row>
+    <row r="103" spans="1:4" ht="30" customHeight="1">
+      <c r="A103" s="1" t="s">
         <v>105</v>
       </c>
-      <c r="B103" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="104" spans="1:4" hidden="1">
-      <c r="A104" t="s">
+      <c r="B103" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C103" s="1"/>
+      <c r="D103" s="1"/>
+    </row>
+    <row r="104" spans="1:4" ht="30" customHeight="1">
+      <c r="A104" s="1" t="s">
         <v>106</v>
       </c>
-      <c r="B104" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="105" spans="1:4" hidden="1">
-      <c r="A105" t="s">
+      <c r="B104" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C104" s="1"/>
+      <c r="D104" s="1"/>
+    </row>
+    <row r="105" spans="1:4" ht="30" customHeight="1">
+      <c r="A105" s="1" t="s">
         <v>107</v>
       </c>
-      <c r="B105" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="106" spans="1:4" hidden="1">
-      <c r="A106" t="s">
+      <c r="B105" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C105" s="1"/>
+      <c r="D105" s="1"/>
+    </row>
+    <row r="106" spans="1:4" ht="30" customHeight="1">
+      <c r="A106" s="1" t="s">
         <v>108</v>
       </c>
-      <c r="B106" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="107" spans="1:4" hidden="1">
-      <c r="A107" t="s">
+      <c r="B106" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C106" s="1"/>
+      <c r="D106" s="1"/>
+    </row>
+    <row r="107" spans="1:4" ht="30" customHeight="1">
+      <c r="A107" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="B107" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="108" spans="1:4" hidden="1">
-      <c r="A108" t="s">
+      <c r="B107" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C107" s="1"/>
+      <c r="D107" s="1"/>
+    </row>
+    <row r="108" spans="1:4" ht="30" customHeight="1">
+      <c r="A108" s="1" t="s">
         <v>110</v>
       </c>
-      <c r="B108" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="109" spans="1:4" hidden="1">
-      <c r="A109" t="s">
+      <c r="B108" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C108" s="1"/>
+      <c r="D108" s="1"/>
+    </row>
+    <row r="109" spans="1:4" ht="30" customHeight="1">
+      <c r="A109" s="1" t="s">
         <v>111</v>
       </c>
-      <c r="B109" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="110" spans="1:4" hidden="1">
-      <c r="A110" t="s">
+      <c r="B109" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C109" s="1"/>
+      <c r="D109" s="1"/>
+    </row>
+    <row r="110" spans="1:4" ht="30" customHeight="1">
+      <c r="A110" s="1" t="s">
         <v>112</v>
       </c>
-      <c r="B110" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="111" spans="1:4" hidden="1">
-      <c r="A111" t="s">
+      <c r="B110" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C110" s="1"/>
+      <c r="D110" s="1"/>
+    </row>
+    <row r="111" spans="1:4" ht="30" customHeight="1">
+      <c r="A111" s="1" t="s">
         <v>113</v>
       </c>
-      <c r="B111" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="112" spans="1:4" hidden="1">
-      <c r="A112" t="s">
+      <c r="B111" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C111" s="1"/>
+      <c r="D111" s="1"/>
+    </row>
+    <row r="112" spans="1:4" ht="30" customHeight="1">
+      <c r="A112" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="B112" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="113" spans="1:2" hidden="1">
-      <c r="A113" t="s">
+      <c r="B112" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C112" s="1"/>
+      <c r="D112" s="1"/>
+    </row>
+    <row r="113" spans="1:4" ht="30" customHeight="1">
+      <c r="A113" s="1" t="s">
         <v>115</v>
       </c>
-      <c r="B113" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="114" spans="1:2" hidden="1">
-      <c r="A114" t="s">
+      <c r="B113" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C113" s="1"/>
+      <c r="D113" s="1"/>
+    </row>
+    <row r="114" spans="1:4" ht="30" customHeight="1">
+      <c r="A114" s="1" t="s">
         <v>116</v>
       </c>
-      <c r="B114" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="115" spans="1:2" hidden="1">
-      <c r="A115" t="s">
+      <c r="B114" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C114" s="1"/>
+      <c r="D114" s="1"/>
+    </row>
+    <row r="115" spans="1:4" ht="30" customHeight="1">
+      <c r="A115" s="1" t="s">
         <v>117</v>
       </c>
-      <c r="B115" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="116" spans="1:2" hidden="1">
-      <c r="A116" t="s">
+      <c r="B115" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C115" s="1"/>
+      <c r="D115" s="1"/>
+    </row>
+    <row r="116" spans="1:4" ht="30" customHeight="1">
+      <c r="A116" s="1" t="s">
         <v>118</v>
       </c>
-      <c r="B116" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="117" spans="1:2" hidden="1">
-      <c r="A117" t="s">
+      <c r="B116" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C116" s="1"/>
+      <c r="D116" s="1"/>
+    </row>
+    <row r="117" spans="1:4" ht="30" customHeight="1">
+      <c r="A117" s="1" t="s">
         <v>199</v>
       </c>
-      <c r="B117" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="118" spans="1:2" hidden="1">
-      <c r="A118" t="s">
+      <c r="B117" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C117" s="1"/>
+      <c r="D117" s="1"/>
+    </row>
+    <row r="118" spans="1:4" ht="30" customHeight="1">
+      <c r="A118" s="1" t="s">
         <v>119</v>
       </c>
-      <c r="B118" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="119" spans="1:2" hidden="1">
-      <c r="A119" t="s">
+      <c r="B118" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C118" s="1"/>
+      <c r="D118" s="1"/>
+    </row>
+    <row r="119" spans="1:4" ht="30" customHeight="1">
+      <c r="A119" s="1" t="s">
         <v>198</v>
       </c>
-      <c r="B119" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="120" spans="1:2" hidden="1">
-      <c r="A120" t="s">
+      <c r="B119" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C119" s="1"/>
+      <c r="D119" s="1"/>
+    </row>
+    <row r="120" spans="1:4" ht="30" customHeight="1">
+      <c r="A120" s="1" t="s">
         <v>120</v>
       </c>
-      <c r="B120" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="121" spans="1:2" hidden="1">
-      <c r="A121" t="s">
+      <c r="B120" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C120" s="1"/>
+      <c r="D120" s="1"/>
+    </row>
+    <row r="121" spans="1:4" ht="30" customHeight="1">
+      <c r="A121" s="1" t="s">
         <v>121</v>
       </c>
-      <c r="B121" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="122" spans="1:2" hidden="1">
-      <c r="A122" t="s">
+      <c r="B121" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C121" s="1"/>
+      <c r="D121" s="1"/>
+    </row>
+    <row r="122" spans="1:4" ht="30" customHeight="1">
+      <c r="A122" s="1" t="s">
         <v>122</v>
       </c>
-      <c r="B122" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="123" spans="1:2" hidden="1">
-      <c r="A123" t="s">
+      <c r="B122" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C122" s="1"/>
+      <c r="D122" s="1"/>
+    </row>
+    <row r="123" spans="1:4" ht="30" customHeight="1">
+      <c r="A123" s="1" t="s">
         <v>123</v>
       </c>
-      <c r="B123" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="124" spans="1:2" hidden="1">
-      <c r="A124" t="s">
+      <c r="B123" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C123" s="1"/>
+      <c r="D123" s="1"/>
+    </row>
+    <row r="124" spans="1:4" ht="30" customHeight="1">
+      <c r="A124" s="1" t="s">
         <v>124</v>
       </c>
-      <c r="B124" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="125" spans="1:2" hidden="1">
-      <c r="A125" t="s">
+      <c r="B124" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C124" s="1"/>
+      <c r="D124" s="1"/>
+    </row>
+    <row r="125" spans="1:4" ht="30" customHeight="1">
+      <c r="A125" s="1" t="s">
         <v>125</v>
       </c>
-      <c r="B125" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="126" spans="1:2" hidden="1">
-      <c r="A126" t="s">
+      <c r="B125" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C125" s="1"/>
+      <c r="D125" s="1"/>
+    </row>
+    <row r="126" spans="1:4" ht="30" customHeight="1">
+      <c r="A126" s="1" t="s">
         <v>126</v>
       </c>
-      <c r="B126" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="127" spans="1:2" hidden="1">
-      <c r="A127" t="s">
+      <c r="B126" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C126" s="1"/>
+      <c r="D126" s="1"/>
+    </row>
+    <row r="127" spans="1:4" ht="30" customHeight="1">
+      <c r="A127" s="1" t="s">
         <v>127</v>
       </c>
-      <c r="B127" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="128" spans="1:2" hidden="1">
-      <c r="A128" t="s">
+      <c r="B127" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C127" s="1"/>
+      <c r="D127" s="1"/>
+    </row>
+    <row r="128" spans="1:4" ht="30" customHeight="1">
+      <c r="A128" s="1" t="s">
         <v>128</v>
       </c>
-      <c r="B128" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="129" spans="1:4" ht="20.100000000000001" customHeight="1">
+      <c r="B128" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C128" s="1"/>
+      <c r="D128" s="1"/>
+    </row>
+    <row r="129" spans="1:4" ht="30" customHeight="1">
       <c r="A129" s="1" t="s">
         <v>129</v>
       </c>
@@ -2455,7 +2656,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="130" spans="1:4" ht="20.100000000000001" customHeight="1">
+    <row r="130" spans="1:4" ht="30" customHeight="1">
       <c r="A130" s="1" t="s">
         <v>130</v>
       </c>
@@ -2469,7 +2670,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="131" spans="1:4" ht="20.100000000000001" customHeight="1">
+    <row r="131" spans="1:4" ht="30" customHeight="1">
       <c r="A131" s="1" t="s">
         <v>131</v>
       </c>
@@ -2483,7 +2684,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="132" spans="1:4" ht="20.100000000000001" customHeight="1">
+    <row r="132" spans="1:4" ht="30" customHeight="1">
       <c r="A132" s="1" t="s">
         <v>132</v>
       </c>
@@ -2497,7 +2698,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="133" spans="1:4" ht="20.100000000000001" customHeight="1">
+    <row r="133" spans="1:4" ht="30" customHeight="1">
       <c r="A133" s="1" t="s">
         <v>133</v>
       </c>
@@ -2511,7 +2712,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="134" spans="1:4" ht="20.100000000000001" customHeight="1">
+    <row r="134" spans="1:4" ht="30" customHeight="1">
       <c r="A134" s="1" t="s">
         <v>134</v>
       </c>
@@ -2525,23 +2726,27 @@
         <v>225</v>
       </c>
     </row>
-    <row r="135" spans="1:4" hidden="1">
-      <c r="A135" t="s">
+    <row r="135" spans="1:4" ht="30" customHeight="1">
+      <c r="A135" s="1" t="s">
         <v>197</v>
       </c>
-      <c r="B135" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="136" spans="1:4" hidden="1">
-      <c r="A136" t="s">
+      <c r="B135" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C135" s="1"/>
+      <c r="D135" s="1"/>
+    </row>
+    <row r="136" spans="1:4" ht="30" customHeight="1">
+      <c r="A136" s="1" t="s">
         <v>196</v>
       </c>
-      <c r="B136" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="137" spans="1:4" ht="20.100000000000001" customHeight="1">
+      <c r="B136" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C136" s="1"/>
+      <c r="D136" s="1"/>
+    </row>
+    <row r="137" spans="1:4" ht="30" customHeight="1">
       <c r="A137" s="1" t="s">
         <v>135</v>
       </c>
@@ -2555,7 +2760,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="138" spans="1:4" ht="20.100000000000001" customHeight="1">
+    <row r="138" spans="1:4" ht="30" customHeight="1">
       <c r="A138" s="1" t="s">
         <v>136</v>
       </c>
@@ -2569,7 +2774,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="139" spans="1:4" ht="20.100000000000001" customHeight="1">
+    <row r="139" spans="1:4" ht="30" customHeight="1">
       <c r="A139" s="1" t="s">
         <v>137</v>
       </c>
@@ -2583,7 +2788,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="140" spans="1:4" ht="20.100000000000001" customHeight="1">
+    <row r="140" spans="1:4" ht="30" customHeight="1">
       <c r="A140" s="1" t="s">
         <v>138</v>
       </c>
@@ -2597,7 +2802,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="141" spans="1:4" ht="20.100000000000001" customHeight="1">
+    <row r="141" spans="1:4" ht="30" customHeight="1">
       <c r="A141" s="1" t="s">
         <v>139</v>
       </c>
@@ -2611,7 +2816,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="142" spans="1:4" ht="20.100000000000001" customHeight="1">
+    <row r="142" spans="1:4" ht="30" customHeight="1">
       <c r="A142" s="1" t="s">
         <v>140</v>
       </c>
@@ -2625,7 +2830,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="143" spans="1:4" ht="20.100000000000001" customHeight="1">
+    <row r="143" spans="1:4" ht="30" customHeight="1">
       <c r="A143" s="1" t="s">
         <v>141</v>
       </c>
@@ -2639,7 +2844,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="144" spans="1:4" ht="20.100000000000001" customHeight="1">
+    <row r="144" spans="1:4" ht="30" customHeight="1">
       <c r="A144" s="1" t="s">
         <v>142</v>
       </c>
@@ -2653,7 +2858,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="145" spans="1:4" ht="20.100000000000001" customHeight="1">
+    <row r="145" spans="1:4" ht="30" customHeight="1">
       <c r="A145" s="1" t="s">
         <v>143</v>
       </c>
@@ -2667,7 +2872,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="146" spans="1:4" ht="20.100000000000001" customHeight="1">
+    <row r="146" spans="1:4" ht="30" customHeight="1">
       <c r="A146" s="1" t="s">
         <v>144</v>
       </c>
@@ -2681,39 +2886,47 @@
         <v>225</v>
       </c>
     </row>
-    <row r="147" spans="1:4" hidden="1">
-      <c r="A147" t="s">
+    <row r="147" spans="1:4" ht="30" customHeight="1">
+      <c r="A147" s="1" t="s">
         <v>145</v>
       </c>
-      <c r="B147" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="148" spans="1:4" hidden="1">
-      <c r="A148" t="s">
+      <c r="B147" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C147" s="1"/>
+      <c r="D147" s="1"/>
+    </row>
+    <row r="148" spans="1:4" ht="30" customHeight="1">
+      <c r="A148" s="1" t="s">
         <v>195</v>
       </c>
-      <c r="B148" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="149" spans="1:4" hidden="1">
-      <c r="A149" t="s">
+      <c r="B148" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C148" s="1"/>
+      <c r="D148" s="1"/>
+    </row>
+    <row r="149" spans="1:4" ht="30" customHeight="1">
+      <c r="A149" s="1" t="s">
         <v>146</v>
       </c>
-      <c r="B149" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="150" spans="1:4" hidden="1">
-      <c r="A150" t="s">
+      <c r="B149" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C149" s="1"/>
+      <c r="D149" s="1"/>
+    </row>
+    <row r="150" spans="1:4" ht="30" customHeight="1">
+      <c r="A150" s="1" t="s">
         <v>147</v>
       </c>
-      <c r="B150" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="151" spans="1:4" ht="20.100000000000001" customHeight="1">
+      <c r="B150" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C150" s="1"/>
+      <c r="D150" s="1"/>
+    </row>
+    <row r="151" spans="1:4" ht="30" customHeight="1">
       <c r="A151" s="1" t="s">
         <v>148</v>
       </c>
@@ -2727,7 +2940,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="152" spans="1:4" ht="20.100000000000001" customHeight="1">
+    <row r="152" spans="1:4" ht="30" customHeight="1">
       <c r="A152" s="1" t="s">
         <v>194</v>
       </c>
@@ -2741,7 +2954,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="153" spans="1:4" ht="20.100000000000001" customHeight="1">
+    <row r="153" spans="1:4" ht="30" customHeight="1">
       <c r="A153" s="1" t="s">
         <v>193</v>
       </c>
@@ -2755,31 +2968,37 @@
         <v>225</v>
       </c>
     </row>
-    <row r="154" spans="1:4" hidden="1">
-      <c r="A154" t="s">
+    <row r="154" spans="1:4" ht="30" customHeight="1">
+      <c r="A154" s="1" t="s">
         <v>191</v>
       </c>
-      <c r="B154" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="155" spans="1:4" hidden="1">
-      <c r="A155" t="s">
+      <c r="B154" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C154" s="1"/>
+      <c r="D154" s="1"/>
+    </row>
+    <row r="155" spans="1:4" ht="30" customHeight="1">
+      <c r="A155" s="1" t="s">
         <v>192</v>
       </c>
-      <c r="B155" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="156" spans="1:4" hidden="1">
-      <c r="A156" t="s">
+      <c r="B155" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C155" s="1"/>
+      <c r="D155" s="1"/>
+    </row>
+    <row r="156" spans="1:4" ht="30" customHeight="1">
+      <c r="A156" s="1" t="s">
         <v>190</v>
       </c>
-      <c r="B156" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="157" spans="1:4" ht="20.100000000000001" customHeight="1">
+      <c r="B156" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C156" s="1"/>
+      <c r="D156" s="1"/>
+    </row>
+    <row r="157" spans="1:4" ht="30" customHeight="1">
       <c r="A157" s="1" t="s">
         <v>149</v>
       </c>
@@ -2793,7 +3012,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="158" spans="1:4" ht="20.100000000000001" customHeight="1">
+    <row r="158" spans="1:4" ht="30" customHeight="1">
       <c r="A158" s="1" t="s">
         <v>150</v>
       </c>
@@ -2807,7 +3026,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="159" spans="1:4" ht="20.100000000000001" customHeight="1">
+    <row r="159" spans="1:4" ht="30" customHeight="1">
       <c r="A159" s="1" t="s">
         <v>189</v>
       </c>
@@ -2821,55 +3040,91 @@
         <v>225</v>
       </c>
     </row>
-    <row r="160" spans="1:4" hidden="1">
-      <c r="A160" t="s">
+    <row r="160" spans="1:4" ht="30" customHeight="1">
+      <c r="A160" s="1" t="s">
         <v>151</v>
       </c>
-      <c r="B160" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="161" spans="1:4" hidden="1">
-      <c r="A161" t="s">
+      <c r="B160" s="1" t="s">
+        <v>230</v>
+      </c>
+      <c r="C160" s="1" t="s">
+        <v>209</v>
+      </c>
+      <c r="D160" s="1" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="161" spans="1:4" ht="30" customHeight="1">
+      <c r="A161" s="1" t="s">
         <v>152</v>
       </c>
-      <c r="B161" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="162" spans="1:4" hidden="1">
-      <c r="A162" t="s">
+      <c r="B161" s="1" t="s">
+        <v>230</v>
+      </c>
+      <c r="C161" s="1" t="s">
+        <v>209</v>
+      </c>
+      <c r="D161" s="1" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="162" spans="1:4" ht="30" customHeight="1">
+      <c r="A162" s="1" t="s">
         <v>188</v>
       </c>
-      <c r="B162" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="163" spans="1:4" hidden="1">
-      <c r="A163" t="s">
+      <c r="B162" s="1" t="s">
+        <v>230</v>
+      </c>
+      <c r="C162" s="1" t="s">
+        <v>209</v>
+      </c>
+      <c r="D162" s="1" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="163" spans="1:4" ht="30" customHeight="1">
+      <c r="A163" s="1" t="s">
         <v>187</v>
       </c>
-      <c r="B163" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="164" spans="1:4" hidden="1">
-      <c r="A164" t="s">
+      <c r="B163" s="1" t="s">
+        <v>230</v>
+      </c>
+      <c r="C163" s="1" t="s">
+        <v>209</v>
+      </c>
+      <c r="D163" s="1" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="164" spans="1:4" ht="30" customHeight="1">
+      <c r="A164" s="1" t="s">
         <v>186</v>
       </c>
-      <c r="B164" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="165" spans="1:4" hidden="1">
-      <c r="A165" t="s">
+      <c r="B164" s="1" t="s">
+        <v>230</v>
+      </c>
+      <c r="C164" s="1" t="s">
+        <v>209</v>
+      </c>
+      <c r="D164" s="1" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="165" spans="1:4" ht="30" customHeight="1">
+      <c r="A165" s="1" t="s">
         <v>185</v>
       </c>
-      <c r="B165" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="166" spans="1:4" ht="20.100000000000001" customHeight="1">
+      <c r="B165" s="1" t="s">
+        <v>230</v>
+      </c>
+      <c r="C165" s="1" t="s">
+        <v>209</v>
+      </c>
+      <c r="D165" s="1" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="166" spans="1:4" ht="30" customHeight="1">
       <c r="A166" s="1" t="s">
         <v>184</v>
       </c>
@@ -2883,7 +3138,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="167" spans="1:4" ht="20.100000000000001" customHeight="1">
+    <row r="167" spans="1:4" ht="30" customHeight="1">
       <c r="A167" s="1" t="s">
         <v>153</v>
       </c>
@@ -2897,7 +3152,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="168" spans="1:4" ht="20.100000000000001" customHeight="1">
+    <row r="168" spans="1:4" ht="30" customHeight="1">
       <c r="A168" s="1" t="s">
         <v>183</v>
       </c>
@@ -2911,7 +3166,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="169" spans="1:4" ht="20.100000000000001" customHeight="1">
+    <row r="169" spans="1:4" ht="30" customHeight="1">
       <c r="A169" s="1" t="s">
         <v>154</v>
       </c>
@@ -2925,7 +3180,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="170" spans="1:4" ht="20.100000000000001" customHeight="1">
+    <row r="170" spans="1:4" ht="30" customHeight="1">
       <c r="A170" s="1" t="s">
         <v>155</v>
       </c>
@@ -2939,15 +3194,17 @@
         <v>225</v>
       </c>
     </row>
-    <row r="171" spans="1:4" hidden="1">
-      <c r="A171" t="s">
+    <row r="171" spans="1:4" ht="30" customHeight="1">
+      <c r="A171" s="1" t="s">
         <v>182</v>
       </c>
-      <c r="B171" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="172" spans="1:4" ht="20.100000000000001" customHeight="1">
+      <c r="B171" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C171" s="1"/>
+      <c r="D171" s="1"/>
+    </row>
+    <row r="172" spans="1:4" ht="30" customHeight="1">
       <c r="A172" s="1" t="s">
         <v>156</v>
       </c>
@@ -2961,15 +3218,17 @@
         <v>225</v>
       </c>
     </row>
-    <row r="173" spans="1:4" hidden="1">
-      <c r="A173" t="s">
+    <row r="173" spans="1:4" ht="30" customHeight="1">
+      <c r="A173" s="1" t="s">
         <v>181</v>
       </c>
-      <c r="B173" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="174" spans="1:4" ht="20.100000000000001" customHeight="1">
+      <c r="B173" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C173" s="1"/>
+      <c r="D173" s="1"/>
+    </row>
+    <row r="174" spans="1:4" ht="30" customHeight="1">
       <c r="A174" s="1" t="s">
         <v>157</v>
       </c>
@@ -2983,7 +3242,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="175" spans="1:4" ht="20.100000000000001" customHeight="1">
+    <row r="175" spans="1:4" ht="30" customHeight="1">
       <c r="A175" s="1" t="s">
         <v>158</v>
       </c>
@@ -2997,23 +3256,27 @@
         <v>225</v>
       </c>
     </row>
-    <row r="176" spans="1:4" hidden="1">
-      <c r="A176" t="s">
+    <row r="176" spans="1:4" ht="30" customHeight="1">
+      <c r="A176" s="1" t="s">
         <v>180</v>
       </c>
-      <c r="B176" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="177" spans="1:4" hidden="1">
-      <c r="A177" t="s">
+      <c r="B176" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C176" s="1"/>
+      <c r="D176" s="1"/>
+    </row>
+    <row r="177" spans="1:4" ht="30" customHeight="1">
+      <c r="A177" s="1" t="s">
         <v>179</v>
       </c>
-      <c r="B177" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="178" spans="1:4" ht="20.100000000000001" customHeight="1">
+      <c r="B177" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C177" s="1"/>
+      <c r="D177" s="1"/>
+    </row>
+    <row r="178" spans="1:4" ht="30" customHeight="1">
       <c r="A178" s="1" t="s">
         <v>177</v>
       </c>
@@ -3027,29 +3290,29 @@
         <v>225</v>
       </c>
     </row>
-    <row r="179" spans="1:4" hidden="1">
-      <c r="A179" t="s">
+    <row r="179" spans="1:4" ht="30" customHeight="1">
+      <c r="A179" s="1" t="s">
         <v>178</v>
       </c>
-      <c r="B179" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="180" spans="1:4" hidden="1">
-      <c r="A180" t="s">
+      <c r="B179" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C179" s="1"/>
+      <c r="D179" s="1"/>
+    </row>
+    <row r="180" spans="1:4" ht="30" customHeight="1">
+      <c r="A180" s="1" t="s">
         <v>159</v>
       </c>
-      <c r="B180" t="s">
-        <v>22</v>
-      </c>
+      <c r="B180" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C180" s="1"/>
+      <c r="D180" s="1"/>
     </row>
   </sheetData>
   <autoFilter ref="B1:B180">
-    <filterColumn colId="0">
-      <filters>
-        <filter val="是"/>
-      </filters>
-    </filterColumn>
+    <filterColumn colId="0"/>
   </autoFilter>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/internal_doc/05.测试设计/story/mysql连接器/5.7.24测试用例差别.xlsx
+++ b/internal_doc/05.测试设计/story/mysql连接器/5.7.24测试用例差别.xlsx
@@ -11,10 +11,11 @@
     <sheet name="5.7.24_suite.json修改" sheetId="2" r:id="rId2"/>
     <sheet name="5.7.18删除" sheetId="3" r:id="rId3"/>
     <sheet name="5.7.24新增" sheetId="4" r:id="rId4"/>
+    <sheet name="Sheet1" sheetId="5" r:id="rId5"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'5.7.24_suite.json修改'!$B$1:$B$7</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'5.7.24_suite.main修改'!$B$1:$B$180</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'5.7.24_suite.main修改'!$B$1:$B$179</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'5.7.24新增'!$B$1:$B$15</definedName>
   </definedNames>
   <calcPr calcId="124519"/>
@@ -22,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="569" uniqueCount="251">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="565" uniqueCount="250">
   <si>
     <t>r</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -156,730 +157,727 @@
     <t>ddl_i18n_utf8.result</t>
   </si>
   <si>
+    <t>derived.result</t>
+  </si>
+  <si>
+    <t>flush_read_lock.result</t>
+  </si>
+  <si>
+    <t>fulltext.result</t>
+  </si>
+  <si>
+    <t>func_gconcat.result</t>
+  </si>
+  <si>
+    <t>func_group.result</t>
+  </si>
+  <si>
+    <t>func_in_icp.result</t>
+  </si>
+  <si>
+    <t>func_in_icp_mrr.result</t>
+  </si>
+  <si>
+    <t>func_in_mrr.result</t>
+  </si>
+  <si>
+    <t>func_in_mrr_cost.result</t>
+  </si>
+  <si>
+    <t>func_in_none.result</t>
+  </si>
+  <si>
+    <t>func_math.result</t>
+  </si>
+  <si>
+    <t>gis.result</t>
+  </si>
+  <si>
+    <t>gis-precise.result</t>
+  </si>
+  <si>
+    <t>gis-rtree.result</t>
+  </si>
+  <si>
+    <t>grant.result</t>
+  </si>
+  <si>
+    <t>grant_alter_user_qa.result</t>
+  </si>
+  <si>
+    <t>grant_cache.result</t>
+  </si>
+  <si>
+    <t>grant_debug.result</t>
+  </si>
+  <si>
+    <t>grant_user_lock_qa.result</t>
+  </si>
+  <si>
+    <t>grant2.result</t>
+  </si>
+  <si>
+    <t>group_by.result</t>
+  </si>
+  <si>
+    <t>group_min_max.result</t>
+  </si>
+  <si>
+    <t>group_min_max_innodb.result</t>
+  </si>
+  <si>
+    <t>index_merge_intersect_dml.result</t>
+  </si>
+  <si>
+    <t>information_schema.result</t>
+  </si>
+  <si>
+    <t>init_connect.result</t>
+  </si>
+  <si>
+    <t>initialize-bug20350099.result</t>
+  </si>
+  <si>
+    <t>initialize-sha256.result</t>
+  </si>
+  <si>
+    <t>innodb_explain_json_non_select_all.result</t>
+  </si>
+  <si>
+    <t>innodb_explain_json_non_select_none.result</t>
+  </si>
+  <si>
+    <t>innodb_explain_non_select_all.result</t>
+  </si>
+  <si>
+    <t>innodb_explain_non_select_none.result</t>
+  </si>
+  <si>
+    <t>innodb_mrr_all.result</t>
+  </si>
+  <si>
+    <t>innodb_mrr_cost.result</t>
+  </si>
+  <si>
+    <t>innodb_mrr_cost_all.result</t>
+  </si>
+  <si>
+    <t>innodb_mrr_cost_icp.result</t>
+  </si>
+  <si>
+    <t>innodb_mrr_icp.result</t>
+  </si>
+  <si>
+    <t>innodb_mrr_none.result</t>
+  </si>
+  <si>
+    <t>join_outer_bka.result</t>
+  </si>
+  <si>
+    <t>join_outer_bka_nixbnl.result</t>
+  </si>
+  <si>
+    <t>locking_service.result</t>
+  </si>
+  <si>
+    <t>max_statement_time.result</t>
+  </si>
+  <si>
+    <t>mdl_sync.result</t>
+  </si>
+  <si>
+    <t>mix2_myisam.result</t>
+  </si>
+  <si>
+    <t>multi_update.result</t>
+  </si>
+  <si>
+    <t>myisam_explain_json_non_select_all.result</t>
+  </si>
+  <si>
+    <t>myisam_explain_json_non_select_none.result</t>
+  </si>
+  <si>
+    <t>myisam_explain_non_select_all.result</t>
+  </si>
+  <si>
+    <t>myisam_explain_non_select_none.result</t>
+  </si>
+  <si>
+    <t>myisam-blob.result</t>
+  </si>
+  <si>
+    <t>mysql_not_windows.result</t>
+  </si>
+  <si>
+    <t>mysql_upgrade.result</t>
+  </si>
+  <si>
+    <t>mysqladmin.result</t>
+  </si>
+  <si>
+    <t>mysqlcheck.result</t>
+  </si>
+  <si>
+    <t>mysqld--help-notwin.result</t>
+  </si>
+  <si>
+    <t>mysqld--help-win.result</t>
+  </si>
+  <si>
+    <t>mysqldump.result</t>
+  </si>
+  <si>
+    <t>mysqlpump.result</t>
+  </si>
+  <si>
+    <t>mysqlpump_basic.result</t>
+  </si>
+  <si>
+    <t>mysqltest.result</t>
+  </si>
+  <si>
+    <t>olap.result</t>
+  </si>
+  <si>
+    <t>partition.result</t>
+  </si>
+  <si>
+    <t>partition_cache.result</t>
+  </si>
+  <si>
+    <t>partition_deprecation.result</t>
+  </si>
+  <si>
+    <t>partition_hash.result</t>
+  </si>
+  <si>
+    <t>partition_innodb.result</t>
+  </si>
+  <si>
+    <t>partition_innodb_tablespace.result</t>
+  </si>
+  <si>
+    <t>partition_list.result</t>
+  </si>
+  <si>
+    <t>partition_locking.result</t>
+  </si>
+  <si>
+    <t>partition_pruning.result</t>
+  </si>
+  <si>
+    <t>partition_range.result</t>
+  </si>
+  <si>
+    <t>plugin_auth.result</t>
+  </si>
+  <si>
+    <t>plugin_auth_qa.result</t>
+  </si>
+  <si>
+    <t>plugin_auth_qa_1.result</t>
+  </si>
+  <si>
+    <t>plugin_auth_qa_2.result</t>
+  </si>
+  <si>
+    <t>plugin_auth_sha256.result</t>
+  </si>
+  <si>
+    <t>plugin_auth_sha256_2.result</t>
+  </si>
+  <si>
+    <t>plugin_auth_sha256_server_default.result</t>
+  </si>
+  <si>
+    <t>plugin_auth_sha256_server_default_tls.result</t>
+  </si>
+  <si>
+    <t>ps_1general.result</t>
+  </si>
+  <si>
+    <t>query_cache_28249.result</t>
+  </si>
+  <si>
+    <t>query_cache_debug.result</t>
+  </si>
+  <si>
+    <t>query_cache_disabled.result</t>
+  </si>
+  <si>
+    <t>query_cache_merge.result</t>
+  </si>
+  <si>
+    <t>query_cache_notembedded.result</t>
+  </si>
+  <si>
+    <t>query_cache_ps_no_prot.result</t>
+  </si>
+  <si>
+    <t>query_cache_size_functionality.result</t>
+  </si>
+  <si>
+    <t>query_cache_type_functionality.result</t>
+  </si>
+  <si>
+    <t>query_cache_with_views.result</t>
+  </si>
+  <si>
+    <t>range_all.result</t>
+  </si>
+  <si>
+    <t>range_icp.result</t>
+  </si>
+  <si>
+    <t>range_icp_mrr.result</t>
+  </si>
+  <si>
+    <t>range_mrr.result</t>
+  </si>
+  <si>
+    <t>range_mrr_cost.result</t>
+  </si>
+  <si>
+    <t>range_none.result</t>
+  </si>
+  <si>
+    <t>select_all.result</t>
+  </si>
+  <si>
+    <t>select_all_bka.result</t>
+  </si>
+  <si>
+    <t>select_all_bka_nixbnl.result</t>
+  </si>
+  <si>
+    <t>select_icp_mrr.result</t>
+  </si>
+  <si>
+    <t>select_icp_mrr_bka.result</t>
+  </si>
+  <si>
+    <t>select_icp_mrr_bka_nixbnl.result</t>
+  </si>
+  <si>
+    <t>select_none.result</t>
+  </si>
+  <si>
+    <t>select_none_bka.result</t>
+  </si>
+  <si>
+    <t>select_none_bka_nixbnl.result</t>
+  </si>
+  <si>
+    <t>select_safe.result</t>
+  </si>
+  <si>
+    <t>session_tracker.result</t>
+  </si>
+  <si>
+    <t>show_check.result</t>
+  </si>
+  <si>
+    <t>signal_demo1.result</t>
+  </si>
+  <si>
+    <t>sp.result</t>
+  </si>
+  <si>
+    <t>subquery_all.result</t>
+  </si>
+  <si>
+    <t>subquery_all_bka.result</t>
+  </si>
+  <si>
+    <t>subquery_nomat_nosj.result</t>
+  </si>
+  <si>
+    <t>subquery_nomat_nosj_bka.result</t>
+  </si>
+  <si>
+    <t>trigger.result</t>
+  </si>
+  <si>
+    <t>type_newdecimal.result</t>
+  </si>
+  <si>
+    <t>type_timestamp.result</t>
+  </si>
+  <si>
+    <t>type_year.result</t>
+  </si>
+  <si>
+    <t>union.result</t>
+  </si>
+  <si>
+    <t>update.result</t>
+  </si>
+  <si>
+    <t>xa.result</t>
+  </si>
+  <si>
+    <t>ansi.result</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>archive_gis.result</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>commit.result</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>concurrent_innodb_safelog.result</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ddl_i18n_koi8r.result</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>deprecate_eof.result</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>events_bugs.result</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>func_misc.result</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ignore_strict.result</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>index_merge_innodb.result</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>initialize.result</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>innodb_mrr.result</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>innodb_mysql_lock2.result</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>innodb_mysql_sync.result</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>key.result</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>loaddata.result</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>varbinary.result</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>variables.result</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>user_var.result</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>user_if_exists.result</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>udf.result</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>type_timestamp_explicit.result</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>trigger_wl3253.result</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>trans_read_only.result</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>subquery_none_bka_nixbnl.result</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>subquery_none_bka.result</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>subquery_none.result</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>subquery_nomat_nosj_bka_nixbnl.result</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>subquery_all_bka_nixbnl.result</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>status.result</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sql_mode.result</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ssl_crl.result</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sp_notembedded.result</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>session_tracker_trx_state.result</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>reset_connection.result</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>range_with_memory_limit.result</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>query_cache.result</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ps.result</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>parser.result</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>odbc.result</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>opt_hints.result</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>log_tables.result</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>lowercase_table_qcache.result</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>metadata.result</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>mdl_tablespace.result</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>m_i_db.result</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>备注</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>测试步骤相同，5.7.24多告警信息</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>测试文件末尾，5.7.24多了测试步骤</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>部分测试步骤预期结果有调整，同时测试文件默认，5.7.24多了测试步骤</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>步骤步骤相同，5.7.24多告警信息及预期结果</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>测试文件末尾，5.7.24多了测试步骤，修改了预期结果</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>测试文件末尾，5.7.24多了测试步骤，修改了预期结果的记录顺序</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>测试步骤相同，5.7.24多插入了一条记录</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>测试文件末尾，5.7.24多了测试步骤，同时多了告警信息</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>测试文件末尾，5.7.24多了测试步骤，同时多了告警信息，修改了预期结果</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>测试步骤相同，5.7.24修改了预期结果</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>测试步骤相同，5.7.24修改了ERROR信息</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>备注</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>修改了预期结果</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>测试文件末尾，5.7.24多了测试步骤</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>修改了测试步骤，测试文件末尾，5.7.24多了测试步骤</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>是否已修改</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>已修改</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>多了一个explain测试步骤，修改了一条执行语句</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>func_in_all.result</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>不需修改用例</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>不需修改，修改了预期结果的步骤由于不支持已屏蔽</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>是</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>否</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>备注</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>验证innodb数据导入功能，不对接</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>否</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>验证upgrade功能，不对接</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>验证dump功能，不对接</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>验证pump功能，不对接</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>no_engine_substitution.test</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>验证no_engine_substitution模式(no_engine_substitution-master.opt)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>测试文件末尾，5.7.24多了测试步骤，新增了parser-master.opt文件</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>验证show_processlist，不对接</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>需要debug版本，暂不对接</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ssl_verify_identity.test</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>验证ssl_mode=verify_identity，暂不对接（ssl_verify_identity-master.opt）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>是</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>事务隔离级别相关，暂不对接，后续需对接（transaction_isolation-master.opt）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>transaction_read_only.test</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>设置tx_read_only为on、off、default时，查询session上的该变量，暂不对接（transaction_read_only-master.opt）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>验证mysql的dump、import等工具的功能，暂时不对接（utility_warnings-master.opt）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>已修改，row_format只支持fixed格式</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
     <t>delete.result</t>
-  </si>
-  <si>
-    <t>derived.result</t>
-  </si>
-  <si>
-    <t>flush_read_lock.result</t>
-  </si>
-  <si>
-    <t>fulltext.result</t>
-  </si>
-  <si>
-    <t>func_gconcat.result</t>
-  </si>
-  <si>
-    <t>func_group.result</t>
-  </si>
-  <si>
-    <t>func_in_icp.result</t>
-  </si>
-  <si>
-    <t>func_in_icp_mrr.result</t>
-  </si>
-  <si>
-    <t>func_in_mrr.result</t>
-  </si>
-  <si>
-    <t>func_in_mrr_cost.result</t>
-  </si>
-  <si>
-    <t>func_in_none.result</t>
-  </si>
-  <si>
-    <t>func_math.result</t>
-  </si>
-  <si>
-    <t>gis.result</t>
-  </si>
-  <si>
-    <t>gis-precise.result</t>
-  </si>
-  <si>
-    <t>gis-rtree.result</t>
-  </si>
-  <si>
-    <t>grant.result</t>
-  </si>
-  <si>
-    <t>grant_alter_user_qa.result</t>
-  </si>
-  <si>
-    <t>grant_cache.result</t>
-  </si>
-  <si>
-    <t>grant_debug.result</t>
-  </si>
-  <si>
-    <t>grant_user_lock_qa.result</t>
-  </si>
-  <si>
-    <t>grant2.result</t>
-  </si>
-  <si>
-    <t>group_by.result</t>
-  </si>
-  <si>
-    <t>group_min_max.result</t>
-  </si>
-  <si>
-    <t>group_min_max_innodb.result</t>
-  </si>
-  <si>
-    <t>index_merge_intersect_dml.result</t>
-  </si>
-  <si>
-    <t>information_schema.result</t>
-  </si>
-  <si>
-    <t>init_connect.result</t>
-  </si>
-  <si>
-    <t>initialize-bug20350099.result</t>
-  </si>
-  <si>
-    <t>initialize-sha256.result</t>
-  </si>
-  <si>
-    <t>innodb_explain_json_non_select_all.result</t>
-  </si>
-  <si>
-    <t>innodb_explain_json_non_select_none.result</t>
-  </si>
-  <si>
-    <t>innodb_explain_non_select_all.result</t>
-  </si>
-  <si>
-    <t>innodb_explain_non_select_none.result</t>
-  </si>
-  <si>
-    <t>innodb_mrr_all.result</t>
-  </si>
-  <si>
-    <t>innodb_mrr_cost.result</t>
-  </si>
-  <si>
-    <t>innodb_mrr_cost_all.result</t>
-  </si>
-  <si>
-    <t>innodb_mrr_cost_icp.result</t>
-  </si>
-  <si>
-    <t>innodb_mrr_icp.result</t>
-  </si>
-  <si>
-    <t>innodb_mrr_none.result</t>
-  </si>
-  <si>
-    <t>join_outer_bka.result</t>
-  </si>
-  <si>
-    <t>join_outer_bka_nixbnl.result</t>
-  </si>
-  <si>
-    <t>locking_service.result</t>
-  </si>
-  <si>
-    <t>max_statement_time.result</t>
-  </si>
-  <si>
-    <t>mdl_sync.result</t>
-  </si>
-  <si>
-    <t>mix2_myisam.result</t>
-  </si>
-  <si>
-    <t>multi_update.result</t>
-  </si>
-  <si>
-    <t>myisam_explain_json_non_select_all.result</t>
-  </si>
-  <si>
-    <t>myisam_explain_json_non_select_none.result</t>
-  </si>
-  <si>
-    <t>myisam_explain_non_select_all.result</t>
-  </si>
-  <si>
-    <t>myisam_explain_non_select_none.result</t>
-  </si>
-  <si>
-    <t>myisam-blob.result</t>
-  </si>
-  <si>
-    <t>mysql_not_windows.result</t>
-  </si>
-  <si>
-    <t>mysql_upgrade.result</t>
-  </si>
-  <si>
-    <t>mysqladmin.result</t>
-  </si>
-  <si>
-    <t>mysqlcheck.result</t>
-  </si>
-  <si>
-    <t>mysqld--help-notwin.result</t>
-  </si>
-  <si>
-    <t>mysqld--help-win.result</t>
-  </si>
-  <si>
-    <t>mysqldump.result</t>
-  </si>
-  <si>
-    <t>mysqlpump.result</t>
-  </si>
-  <si>
-    <t>mysqlpump_basic.result</t>
-  </si>
-  <si>
-    <t>mysqltest.result</t>
-  </si>
-  <si>
-    <t>olap.result</t>
-  </si>
-  <si>
-    <t>partition.result</t>
-  </si>
-  <si>
-    <t>partition_cache.result</t>
-  </si>
-  <si>
-    <t>partition_deprecation.result</t>
-  </si>
-  <si>
-    <t>partition_hash.result</t>
-  </si>
-  <si>
-    <t>partition_innodb.result</t>
-  </si>
-  <si>
-    <t>partition_innodb_tablespace.result</t>
-  </si>
-  <si>
-    <t>partition_list.result</t>
-  </si>
-  <si>
-    <t>partition_locking.result</t>
-  </si>
-  <si>
-    <t>partition_pruning.result</t>
-  </si>
-  <si>
-    <t>partition_range.result</t>
-  </si>
-  <si>
-    <t>plugin_auth.result</t>
-  </si>
-  <si>
-    <t>plugin_auth_qa.result</t>
-  </si>
-  <si>
-    <t>plugin_auth_qa_1.result</t>
-  </si>
-  <si>
-    <t>plugin_auth_qa_2.result</t>
-  </si>
-  <si>
-    <t>plugin_auth_sha256.result</t>
-  </si>
-  <si>
-    <t>plugin_auth_sha256_2.result</t>
-  </si>
-  <si>
-    <t>plugin_auth_sha256_server_default.result</t>
-  </si>
-  <si>
-    <t>plugin_auth_sha256_server_default_tls.result</t>
-  </si>
-  <si>
-    <t>ps_1general.result</t>
-  </si>
-  <si>
-    <t>query_cache_28249.result</t>
-  </si>
-  <si>
-    <t>query_cache_debug.result</t>
-  </si>
-  <si>
-    <t>query_cache_disabled.result</t>
-  </si>
-  <si>
-    <t>query_cache_merge.result</t>
-  </si>
-  <si>
-    <t>query_cache_notembedded.result</t>
-  </si>
-  <si>
-    <t>query_cache_ps_no_prot.result</t>
-  </si>
-  <si>
-    <t>query_cache_size_functionality.result</t>
-  </si>
-  <si>
-    <t>query_cache_type_functionality.result</t>
-  </si>
-  <si>
-    <t>query_cache_with_views.result</t>
-  </si>
-  <si>
-    <t>range_all.result</t>
-  </si>
-  <si>
-    <t>range_icp.result</t>
-  </si>
-  <si>
-    <t>range_icp_mrr.result</t>
-  </si>
-  <si>
-    <t>range_mrr.result</t>
-  </si>
-  <si>
-    <t>range_mrr_cost.result</t>
-  </si>
-  <si>
-    <t>range_none.result</t>
-  </si>
-  <si>
-    <t>select_all.result</t>
-  </si>
-  <si>
-    <t>select_all_bka.result</t>
-  </si>
-  <si>
-    <t>select_all_bka_nixbnl.result</t>
-  </si>
-  <si>
-    <t>select_icp_mrr.result</t>
-  </si>
-  <si>
-    <t>select_icp_mrr_bka.result</t>
-  </si>
-  <si>
-    <t>select_icp_mrr_bka_nixbnl.result</t>
-  </si>
-  <si>
-    <t>select_none.result</t>
-  </si>
-  <si>
-    <t>select_none_bka.result</t>
-  </si>
-  <si>
-    <t>select_none_bka_nixbnl.result</t>
-  </si>
-  <si>
-    <t>select_safe.result</t>
-  </si>
-  <si>
-    <t>session_tracker.result</t>
-  </si>
-  <si>
-    <t>show_check.result</t>
-  </si>
-  <si>
-    <t>signal_demo1.result</t>
-  </si>
-  <si>
-    <t>sp.result</t>
-  </si>
-  <si>
-    <t>subquery_all.result</t>
-  </si>
-  <si>
-    <t>subquery_all_bka.result</t>
-  </si>
-  <si>
-    <t>subquery_nomat_nosj.result</t>
-  </si>
-  <si>
-    <t>subquery_nomat_nosj_bka.result</t>
-  </si>
-  <si>
-    <t>trigger.result</t>
-  </si>
-  <si>
-    <t>type_newdecimal.result</t>
-  </si>
-  <si>
-    <t>type_timestamp.result</t>
-  </si>
-  <si>
-    <t>type_year.result</t>
-  </si>
-  <si>
-    <t>union.result</t>
-  </si>
-  <si>
-    <t>update.result</t>
-  </si>
-  <si>
-    <t>xa.result</t>
-  </si>
-  <si>
-    <t>ansi.result</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>archive_gis.result</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>commit.result</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>concurrent_innodb_safelog.result</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ddl_i18n_koi8r.result</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>deprecate_eof.result</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>events_bugs.result</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>func_misc.result</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ignore_strict.result</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>index_merge_innodb.result</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>initialize.result</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>innodb_mrr.result</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>innodb_mysql_lock2.result</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>innodb_mysql_sync.result</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>join_outer.result</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>key.result</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>loaddata.result</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>varbinary.result</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>variables.result</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>user_var.result</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>user_if_exists.result</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>udf.result</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>type_timestamp_explicit.result</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>trigger_wl3253.result</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>trans_read_only.result</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>subquery_none_bka_nixbnl.result</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>subquery_none_bka.result</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>subquery_none.result</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>subquery_nomat_nosj_bka_nixbnl.result</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>subquery_all_bka_nixbnl.result</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>status.result</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>sql_mode.result</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ssl_crl.result</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>sp-error.result</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>sp_notembedded.result</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>session_tracker_trx_state.result</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>reset_connection.result</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>range_with_memory_limit.result</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>query_cache.result</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ps.result</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>parser.result</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>odbc.result</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>opt_hints.result</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>log_tables.result</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>lowercase_table_qcache.result</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>metadata.result</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>mdl_tablespace.result</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>m_i_db.result</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>备注</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>测试步骤相同，5.7.24多告警信息</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>测试文件末尾，5.7.24多了测试步骤</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>部分测试步骤预期结果有调整，同时测试文件默认，5.7.24多了测试步骤</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>步骤步骤相同，5.7.24多告警信息及预期结果</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>测试文件末尾，5.7.24多了测试步骤，修改了预期结果</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>测试文件末尾，5.7.24多了测试步骤，修改了预期结果的记录顺序</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>测试步骤相同，5.7.24多插入了一条记录</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>测试文件末尾，5.7.24多了测试步骤，同时多了告警信息</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>测试文件末尾，5.7.24多了测试步骤，同时多了告警信息，修改了预期结果</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>测试步骤相同，5.7.24修改了预期结果</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>测试步骤相同，5.7.24修改了ERROR信息</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>备注</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>修改了预期结果</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>测试文件末尾，5.7.24多了测试步骤</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>修改了测试步骤，测试文件末尾，5.7.24多了测试步骤</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>是否已修改</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>已修改</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>多了一个explain测试步骤，修改了一条执行语句</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>func_in_all.result</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>不需修改用例</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>不需修改，修改了预期结果的步骤由于不支持已屏蔽</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>是</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>否</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>备注</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>验证innodb数据导入功能，不对接</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>否</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>验证upgrade功能，不对接</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>验证dump功能，不对接</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>验证pump功能，不对接</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>no_engine_substitution.test</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>验证no_engine_substitution模式(no_engine_substitution-master.opt)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>测试文件末尾，5.7.24多了测试步骤，新增了parser-master.opt文件</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>验证show_processlist，不对接</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>需要debug版本，暂不对接</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ssl_verify_identity.test</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>验证ssl_mode=verify_identity，暂不对接（ssl_verify_identity-master.opt）</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>是</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>事务隔离级别相关，暂不对接，后续需对接（transaction_isolation-master.opt）</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>transaction_read_only.test</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>设置tx_read_only为on、off、default时，查询session上的该变量，暂不对接（transaction_read_only-master.opt）</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>验证mysql的dump、import等工具的功能，暂时不对接（utility_warnings-master.opt）</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>已修改，row_format只支持fixed格式</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1245,7 +1243,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D180"/>
+  <dimension ref="A1:D179"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="34.5" customWidth="1"/>
@@ -1262,10 +1260,10 @@
         <v>19</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
     </row>
     <row r="2" spans="1:4" ht="30" customHeight="1">
@@ -1280,21 +1278,21 @@
     </row>
     <row r="3" spans="1:4" ht="30" customHeight="1">
       <c r="A3" s="1" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>21</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
     </row>
     <row r="4" spans="1:4" ht="30" customHeight="1">
       <c r="A4" s="1" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>22</v>
@@ -1310,10 +1308,10 @@
         <v>21</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="30" customHeight="1">
@@ -1338,21 +1336,21 @@
     </row>
     <row r="8" spans="1:4" ht="30" customHeight="1">
       <c r="A8" s="1" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>21</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
     </row>
     <row r="9" spans="1:4" ht="30" customHeight="1">
       <c r="A9" s="1" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>22</v>
@@ -1388,10 +1386,10 @@
         <v>21</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
     </row>
     <row r="13" spans="1:4" ht="30" customHeight="1">
@@ -1402,15 +1400,15 @@
         <v>21</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
     </row>
     <row r="14" spans="1:4" ht="30" customHeight="1">
       <c r="A14" s="1" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="B14" s="1" t="s">
         <v>22</v>
@@ -1430,21 +1428,21 @@
     </row>
     <row r="16" spans="1:4" ht="30" customHeight="1">
       <c r="A16" s="1" t="s">
-        <v>39</v>
+        <v>248</v>
       </c>
       <c r="B16" s="1" t="s">
         <v>21</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
     </row>
     <row r="17" spans="1:4" ht="30" customHeight="1">
       <c r="A17" s="1" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="B17" s="1" t="s">
         <v>22</v>
@@ -1454,7 +1452,7 @@
     </row>
     <row r="18" spans="1:4" ht="30" customHeight="1">
       <c r="A18" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B18" s="1" t="s">
         <v>22</v>
@@ -1464,7 +1462,7 @@
     </row>
     <row r="19" spans="1:4" ht="30" customHeight="1">
       <c r="A19" s="1" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="B19" s="1" t="s">
         <v>22</v>
@@ -1474,7 +1472,7 @@
     </row>
     <row r="20" spans="1:4" ht="30" customHeight="1">
       <c r="A20" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B20" s="1" t="s">
         <v>22</v>
@@ -1484,7 +1482,7 @@
     </row>
     <row r="21" spans="1:4" ht="30" customHeight="1">
       <c r="A21" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B21" s="1" t="s">
         <v>22</v>
@@ -1494,147 +1492,147 @@
     </row>
     <row r="22" spans="1:4" ht="30" customHeight="1">
       <c r="A22" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B22" s="1" t="s">
         <v>21</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
     </row>
     <row r="23" spans="1:4" ht="30" customHeight="1">
       <c r="A23" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B23" s="1" t="s">
         <v>21</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
     </row>
     <row r="24" spans="1:4" ht="30" customHeight="1">
       <c r="A24" s="1" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="B24" s="1" t="s">
         <v>21</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
     </row>
     <row r="25" spans="1:4" ht="30" customHeight="1">
       <c r="A25" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B25" s="1" t="s">
         <v>21</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
     </row>
     <row r="26" spans="1:4" ht="30" customHeight="1">
       <c r="A26" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
     </row>
     <row r="27" spans="1:4" ht="30" customHeight="1">
       <c r="A27" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B27" s="1" t="s">
         <v>21</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
     </row>
     <row r="28" spans="1:4" ht="30" customHeight="1">
       <c r="A28" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B28" s="1" t="s">
         <v>21</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
     </row>
     <row r="29" spans="1:4" ht="30" customHeight="1">
       <c r="A29" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B29" s="1" t="s">
         <v>21</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
     </row>
     <row r="30" spans="1:4" ht="30" customHeight="1">
       <c r="A30" s="1" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B30" s="1" t="s">
         <v>21</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
     </row>
     <row r="31" spans="1:4" ht="30" customHeight="1">
       <c r="A31" s="1" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="B31" s="1" t="s">
         <v>21</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
     </row>
     <row r="32" spans="1:4" ht="30" customHeight="1">
       <c r="A32" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B32" s="1" t="s">
         <v>22</v>
@@ -1644,7 +1642,7 @@
     </row>
     <row r="33" spans="1:4" ht="30" customHeight="1">
       <c r="A33" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B33" s="1" t="s">
         <v>22</v>
@@ -1654,7 +1652,7 @@
     </row>
     <row r="34" spans="1:4" ht="30" customHeight="1">
       <c r="A34" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B34" s="1" t="s">
         <v>22</v>
@@ -1664,7 +1662,7 @@
     </row>
     <row r="35" spans="1:4" ht="30" customHeight="1">
       <c r="A35" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B35" s="1" t="s">
         <v>22</v>
@@ -1674,7 +1672,7 @@
     </row>
     <row r="36" spans="1:4" ht="30" customHeight="1">
       <c r="A36" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B36" s="1" t="s">
         <v>22</v>
@@ -1684,7 +1682,7 @@
     </row>
     <row r="37" spans="1:4" ht="30" customHeight="1">
       <c r="A37" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B37" s="1" t="s">
         <v>22</v>
@@ -1694,7 +1692,7 @@
     </row>
     <row r="38" spans="1:4" ht="30" customHeight="1">
       <c r="A38" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B38" s="1" t="s">
         <v>22</v>
@@ -1704,7 +1702,7 @@
     </row>
     <row r="39" spans="1:4" ht="30" customHeight="1">
       <c r="A39" s="1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B39" s="1" t="s">
         <v>22</v>
@@ -1714,7 +1712,7 @@
     </row>
     <row r="40" spans="1:4" ht="30" customHeight="1">
       <c r="A40" s="1" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B40" s="1" t="s">
         <v>22</v>
@@ -1724,49 +1722,49 @@
     </row>
     <row r="41" spans="1:4" ht="30" customHeight="1">
       <c r="A41" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B41" s="1" t="s">
         <v>21</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
     </row>
     <row r="42" spans="1:4" ht="30" customHeight="1">
       <c r="A42" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B42" s="1" t="s">
         <v>21</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
     </row>
     <row r="43" spans="1:4" ht="30" customHeight="1">
       <c r="A43" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B43" s="1" t="s">
         <v>21</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
     </row>
     <row r="44" spans="1:4" ht="30" customHeight="1">
       <c r="A44" s="1" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="B44" s="1" t="s">
         <v>22</v>
@@ -1776,7 +1774,7 @@
     </row>
     <row r="45" spans="1:4" ht="30" customHeight="1">
       <c r="A45" s="1" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B45" s="1" t="s">
         <v>22</v>
@@ -1786,7 +1784,7 @@
     </row>
     <row r="46" spans="1:4" ht="30" customHeight="1">
       <c r="A46" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B46" s="1" t="s">
         <v>22</v>
@@ -1796,7 +1794,7 @@
     </row>
     <row r="47" spans="1:4" ht="30" customHeight="1">
       <c r="A47" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B47" s="1" t="s">
         <v>22</v>
@@ -1806,7 +1804,7 @@
     </row>
     <row r="48" spans="1:4" ht="30" customHeight="1">
       <c r="A48" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B48" s="1" t="s">
         <v>22</v>
@@ -1816,7 +1814,7 @@
     </row>
     <row r="49" spans="1:4" ht="30" customHeight="1">
       <c r="A49" s="1" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B49" s="1" t="s">
         <v>22</v>
@@ -1826,7 +1824,7 @@
     </row>
     <row r="50" spans="1:4" ht="30" customHeight="1">
       <c r="A50" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B50" s="1" t="s">
         <v>22</v>
@@ -1836,7 +1834,7 @@
     </row>
     <row r="51" spans="1:4" ht="30" customHeight="1">
       <c r="A51" s="1" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B51" s="1" t="s">
         <v>22</v>
@@ -1846,7 +1844,7 @@
     </row>
     <row r="52" spans="1:4" ht="30" customHeight="1">
       <c r="A52" s="1" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B52" s="1" t="s">
         <v>22</v>
@@ -1856,7 +1854,7 @@
     </row>
     <row r="53" spans="1:4" ht="30" customHeight="1">
       <c r="A53" s="1" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B53" s="1" t="s">
         <v>22</v>
@@ -1866,7 +1864,7 @@
     </row>
     <row r="54" spans="1:4" ht="30" customHeight="1">
       <c r="A54" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B54" s="1" t="s">
         <v>22</v>
@@ -1876,7 +1874,7 @@
     </row>
     <row r="55" spans="1:4" ht="30" customHeight="1">
       <c r="A55" s="1" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B55" s="1" t="s">
         <v>22</v>
@@ -1886,7 +1884,7 @@
     </row>
     <row r="56" spans="1:4" ht="30" customHeight="1">
       <c r="A56" s="1" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="B56" s="1" t="s">
         <v>22</v>
@@ -1896,7 +1894,7 @@
     </row>
     <row r="57" spans="1:4" ht="30" customHeight="1">
       <c r="A57" s="1" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B57" s="1" t="s">
         <v>22</v>
@@ -1906,7 +1904,7 @@
     </row>
     <row r="58" spans="1:4" ht="30" customHeight="1">
       <c r="A58" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B58" s="1" t="s">
         <v>22</v>
@@ -1916,7 +1914,7 @@
     </row>
     <row r="59" spans="1:4" ht="30" customHeight="1">
       <c r="A59" s="1" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B59" s="1" t="s">
         <v>22</v>
@@ -1926,7 +1924,7 @@
     </row>
     <row r="60" spans="1:4" ht="30" customHeight="1">
       <c r="A60" s="1" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B60" s="1" t="s">
         <v>22</v>
@@ -1936,7 +1934,7 @@
     </row>
     <row r="61" spans="1:4" ht="30" customHeight="1">
       <c r="A61" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B61" s="1" t="s">
         <v>22</v>
@@ -1946,7 +1944,7 @@
     </row>
     <row r="62" spans="1:4" ht="30" customHeight="1">
       <c r="A62" s="1" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B62" s="1" t="s">
         <v>22</v>
@@ -1956,7 +1954,7 @@
     </row>
     <row r="63" spans="1:4" ht="30" customHeight="1">
       <c r="A63" s="1" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B63" s="1" t="s">
         <v>22</v>
@@ -1966,7 +1964,7 @@
     </row>
     <row r="64" spans="1:4" ht="30" customHeight="1">
       <c r="A64" s="1" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="B64" s="1" t="s">
         <v>22</v>
@@ -1976,63 +1974,63 @@
     </row>
     <row r="65" spans="1:4" ht="30" customHeight="1">
       <c r="A65" s="1" t="s">
-        <v>174</v>
+        <v>249</v>
       </c>
       <c r="B65" s="1" t="s">
         <v>21</v>
       </c>
       <c r="C65" s="1" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="D65" s="1" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
     </row>
     <row r="66" spans="1:4" ht="30" customHeight="1">
       <c r="A66" s="1" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B66" s="1" t="s">
         <v>21</v>
       </c>
       <c r="C66" s="1" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="D66" s="1" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
     </row>
     <row r="67" spans="1:4" ht="30" customHeight="1">
       <c r="A67" s="1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B67" s="1" t="s">
         <v>21</v>
       </c>
       <c r="C67" s="1" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="D67" s="1" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
     </row>
     <row r="68" spans="1:4" ht="30" customHeight="1">
       <c r="A68" s="1" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="B68" s="1" t="s">
         <v>21</v>
       </c>
       <c r="C68" s="1" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="D68" s="1" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
     </row>
     <row r="69" spans="1:4" ht="30" customHeight="1">
       <c r="A69" s="1" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="B69" s="1" t="s">
         <v>22</v>
@@ -2042,7 +2040,7 @@
     </row>
     <row r="70" spans="1:4" ht="30" customHeight="1">
       <c r="A70" s="1" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B70" s="1" t="s">
         <v>22</v>
@@ -2052,7 +2050,7 @@
     </row>
     <row r="71" spans="1:4" ht="30" customHeight="1">
       <c r="A71" s="1" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="B71" s="1" t="s">
         <v>22</v>
@@ -2062,7 +2060,7 @@
     </row>
     <row r="72" spans="1:4" ht="30" customHeight="1">
       <c r="A72" s="1" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="B72" s="1" t="s">
         <v>22</v>
@@ -2072,7 +2070,7 @@
     </row>
     <row r="73" spans="1:4" ht="30" customHeight="1">
       <c r="A73" s="1" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="B73" s="1" t="s">
         <v>22</v>
@@ -2082,7 +2080,7 @@
     </row>
     <row r="74" spans="1:4" ht="30" customHeight="1">
       <c r="A74" s="1" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B74" s="1" t="s">
         <v>22</v>
@@ -2092,7 +2090,7 @@
     </row>
     <row r="75" spans="1:4" ht="30" customHeight="1">
       <c r="A75" s="1" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B75" s="1" t="s">
         <v>22</v>
@@ -2102,7 +2100,7 @@
     </row>
     <row r="76" spans="1:4" ht="30" customHeight="1">
       <c r="A76" s="1" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="B76" s="1" t="s">
         <v>22</v>
@@ -2112,7 +2110,7 @@
     </row>
     <row r="77" spans="1:4" ht="30" customHeight="1">
       <c r="A77" s="1" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="B77" s="1" t="s">
         <v>22</v>
@@ -2122,7 +2120,7 @@
     </row>
     <row r="78" spans="1:4" ht="30" customHeight="1">
       <c r="A78" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B78" s="1" t="s">
         <v>22</v>
@@ -2132,21 +2130,21 @@
     </row>
     <row r="79" spans="1:4" ht="30" customHeight="1">
       <c r="A79" s="1" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B79" s="1" t="s">
         <v>21</v>
       </c>
       <c r="C79" s="1" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="D79" s="1" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
     </row>
     <row r="80" spans="1:4" ht="30" customHeight="1">
       <c r="A80" s="1" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B80" s="1" t="s">
         <v>22</v>
@@ -2156,7 +2154,7 @@
     </row>
     <row r="81" spans="1:4" ht="30" customHeight="1">
       <c r="A81" s="1" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B81" s="1" t="s">
         <v>22</v>
@@ -2166,7 +2164,7 @@
     </row>
     <row r="82" spans="1:4" ht="30" customHeight="1">
       <c r="A82" s="1" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B82" s="1" t="s">
         <v>22</v>
@@ -2176,7 +2174,7 @@
     </row>
     <row r="83" spans="1:4" ht="30" customHeight="1">
       <c r="A83" s="1" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B83" s="1" t="s">
         <v>22</v>
@@ -2186,7 +2184,7 @@
     </row>
     <row r="84" spans="1:4" ht="30" customHeight="1">
       <c r="A84" s="1" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B84" s="1" t="s">
         <v>22</v>
@@ -2196,7 +2194,7 @@
     </row>
     <row r="85" spans="1:4" ht="30" customHeight="1">
       <c r="A85" s="1" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B85" s="1" t="s">
         <v>22</v>
@@ -2206,7 +2204,7 @@
     </row>
     <row r="86" spans="1:4" ht="30" customHeight="1">
       <c r="A86" s="1" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B86" s="1" t="s">
         <v>22</v>
@@ -2216,7 +2214,7 @@
     </row>
     <row r="87" spans="1:4" ht="30" customHeight="1">
       <c r="A87" s="1" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B87" s="1" t="s">
         <v>22</v>
@@ -2226,7 +2224,7 @@
     </row>
     <row r="88" spans="1:4" ht="30" customHeight="1">
       <c r="A88" s="1" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B88" s="1" t="s">
         <v>22</v>
@@ -2236,7 +2234,7 @@
     </row>
     <row r="89" spans="1:4" ht="30" customHeight="1">
       <c r="A89" s="1" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B89" s="1" t="s">
         <v>22</v>
@@ -2246,7 +2244,7 @@
     </row>
     <row r="90" spans="1:4" ht="30" customHeight="1">
       <c r="A90" s="1" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B90" s="1" t="s">
         <v>22</v>
@@ -2256,7 +2254,7 @@
     </row>
     <row r="91" spans="1:4" ht="30" customHeight="1">
       <c r="A91" s="1" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B91" s="1" t="s">
         <v>22</v>
@@ -2266,7 +2264,7 @@
     </row>
     <row r="92" spans="1:4" ht="30" customHeight="1">
       <c r="A92" s="1" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B92" s="1" t="s">
         <v>22</v>
@@ -2276,7 +2274,7 @@
     </row>
     <row r="93" spans="1:4" ht="30" customHeight="1">
       <c r="A93" s="1" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B93" s="1" t="s">
         <v>22</v>
@@ -2286,7 +2284,7 @@
     </row>
     <row r="94" spans="1:4" ht="30" customHeight="1">
       <c r="A94" s="1" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B94" s="1" t="s">
         <v>22</v>
@@ -2296,7 +2294,7 @@
     </row>
     <row r="95" spans="1:4" ht="30" customHeight="1">
       <c r="A95" s="1" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="B95" s="1" t="s">
         <v>22</v>
@@ -2306,21 +2304,21 @@
     </row>
     <row r="96" spans="1:4" ht="30" customHeight="1">
       <c r="A96" s="1" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B96" s="1" t="s">
         <v>21</v>
       </c>
       <c r="C96" s="1" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="D96" s="1" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
     </row>
     <row r="97" spans="1:4" ht="30" customHeight="1">
       <c r="A97" s="1" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="B97" s="1" t="s">
         <v>22</v>
@@ -2330,21 +2328,21 @@
     </row>
     <row r="98" spans="1:4" ht="30" customHeight="1">
       <c r="A98" s="1" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="B98" s="1" t="s">
         <v>21</v>
       </c>
       <c r="C98" s="1" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="D98" s="1" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
     </row>
     <row r="99" spans="1:4" ht="30" customHeight="1">
       <c r="A99" s="1" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B99" s="1" t="s">
         <v>22</v>
@@ -2354,7 +2352,7 @@
     </row>
     <row r="100" spans="1:4" ht="30" customHeight="1">
       <c r="A100" s="1" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B100" s="1" t="s">
         <v>22</v>
@@ -2364,7 +2362,7 @@
     </row>
     <row r="101" spans="1:4" ht="30" customHeight="1">
       <c r="A101" s="1" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B101" s="1" t="s">
         <v>22</v>
@@ -2374,7 +2372,7 @@
     </row>
     <row r="102" spans="1:4" ht="30" customHeight="1">
       <c r="A102" s="1" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B102" s="1" t="s">
         <v>22</v>
@@ -2384,7 +2382,7 @@
     </row>
     <row r="103" spans="1:4" ht="30" customHeight="1">
       <c r="A103" s="1" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B103" s="1" t="s">
         <v>22</v>
@@ -2394,7 +2392,7 @@
     </row>
     <row r="104" spans="1:4" ht="30" customHeight="1">
       <c r="A104" s="1" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B104" s="1" t="s">
         <v>22</v>
@@ -2404,7 +2402,7 @@
     </row>
     <row r="105" spans="1:4" ht="30" customHeight="1">
       <c r="A105" s="1" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B105" s="1" t="s">
         <v>22</v>
@@ -2414,7 +2412,7 @@
     </row>
     <row r="106" spans="1:4" ht="30" customHeight="1">
       <c r="A106" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B106" s="1" t="s">
         <v>22</v>
@@ -2424,7 +2422,7 @@
     </row>
     <row r="107" spans="1:4" ht="30" customHeight="1">
       <c r="A107" s="1" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B107" s="1" t="s">
         <v>22</v>
@@ -2434,7 +2432,7 @@
     </row>
     <row r="108" spans="1:4" ht="30" customHeight="1">
       <c r="A108" s="1" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B108" s="1" t="s">
         <v>22</v>
@@ -2444,7 +2442,7 @@
     </row>
     <row r="109" spans="1:4" ht="30" customHeight="1">
       <c r="A109" s="1" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B109" s="1" t="s">
         <v>22</v>
@@ -2454,7 +2452,7 @@
     </row>
     <row r="110" spans="1:4" ht="30" customHeight="1">
       <c r="A110" s="1" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B110" s="1" t="s">
         <v>22</v>
@@ -2464,7 +2462,7 @@
     </row>
     <row r="111" spans="1:4" ht="30" customHeight="1">
       <c r="A111" s="1" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B111" s="1" t="s">
         <v>22</v>
@@ -2474,7 +2472,7 @@
     </row>
     <row r="112" spans="1:4" ht="30" customHeight="1">
       <c r="A112" s="1" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B112" s="1" t="s">
         <v>22</v>
@@ -2484,7 +2482,7 @@
     </row>
     <row r="113" spans="1:4" ht="30" customHeight="1">
       <c r="A113" s="1" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B113" s="1" t="s">
         <v>22</v>
@@ -2494,7 +2492,7 @@
     </row>
     <row r="114" spans="1:4" ht="30" customHeight="1">
       <c r="A114" s="1" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B114" s="1" t="s">
         <v>22</v>
@@ -2504,7 +2502,7 @@
     </row>
     <row r="115" spans="1:4" ht="30" customHeight="1">
       <c r="A115" s="1" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B115" s="1" t="s">
         <v>22</v>
@@ -2514,7 +2512,7 @@
     </row>
     <row r="116" spans="1:4" ht="30" customHeight="1">
       <c r="A116" s="1" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B116" s="1" t="s">
         <v>22</v>
@@ -2524,7 +2522,7 @@
     </row>
     <row r="117" spans="1:4" ht="30" customHeight="1">
       <c r="A117" s="1" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="B117" s="1" t="s">
         <v>22</v>
@@ -2534,7 +2532,7 @@
     </row>
     <row r="118" spans="1:4" ht="30" customHeight="1">
       <c r="A118" s="1" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B118" s="1" t="s">
         <v>22</v>
@@ -2544,7 +2542,7 @@
     </row>
     <row r="119" spans="1:4" ht="30" customHeight="1">
       <c r="A119" s="1" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="B119" s="1" t="s">
         <v>22</v>
@@ -2554,7 +2552,7 @@
     </row>
     <row r="120" spans="1:4" ht="30" customHeight="1">
       <c r="A120" s="1" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B120" s="1" t="s">
         <v>22</v>
@@ -2564,7 +2562,7 @@
     </row>
     <row r="121" spans="1:4" ht="30" customHeight="1">
       <c r="A121" s="1" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B121" s="1" t="s">
         <v>22</v>
@@ -2574,7 +2572,7 @@
     </row>
     <row r="122" spans="1:4" ht="30" customHeight="1">
       <c r="A122" s="1" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="B122" s="1" t="s">
         <v>22</v>
@@ -2584,7 +2582,7 @@
     </row>
     <row r="123" spans="1:4" ht="30" customHeight="1">
       <c r="A123" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B123" s="1" t="s">
         <v>22</v>
@@ -2594,7 +2592,7 @@
     </row>
     <row r="124" spans="1:4" ht="30" customHeight="1">
       <c r="A124" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="B124" s="1" t="s">
         <v>22</v>
@@ -2604,7 +2602,7 @@
     </row>
     <row r="125" spans="1:4" ht="30" customHeight="1">
       <c r="A125" s="1" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B125" s="1" t="s">
         <v>22</v>
@@ -2614,7 +2612,7 @@
     </row>
     <row r="126" spans="1:4" ht="30" customHeight="1">
       <c r="A126" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B126" s="1" t="s">
         <v>22</v>
@@ -2624,7 +2622,7 @@
     </row>
     <row r="127" spans="1:4" ht="30" customHeight="1">
       <c r="A127" s="1" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="B127" s="1" t="s">
         <v>22</v>
@@ -2634,7 +2632,7 @@
     </row>
     <row r="128" spans="1:4" ht="30" customHeight="1">
       <c r="A128" s="1" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B128" s="1" t="s">
         <v>22</v>
@@ -2644,91 +2642,91 @@
     </row>
     <row r="129" spans="1:4" ht="30" customHeight="1">
       <c r="A129" s="1" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B129" s="1" t="s">
         <v>21</v>
       </c>
       <c r="C129" s="1" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="D129" s="1" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
     </row>
     <row r="130" spans="1:4" ht="30" customHeight="1">
       <c r="A130" s="1" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="B130" s="1" t="s">
         <v>21</v>
       </c>
       <c r="C130" s="1" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="D130" s="1" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
     </row>
     <row r="131" spans="1:4" ht="30" customHeight="1">
       <c r="A131" s="1" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B131" s="1" t="s">
         <v>21</v>
       </c>
       <c r="C131" s="1" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="D131" s="1" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
     </row>
     <row r="132" spans="1:4" ht="30" customHeight="1">
       <c r="A132" s="1" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B132" s="1" t="s">
         <v>21</v>
       </c>
       <c r="C132" s="1" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="D132" s="1" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
     </row>
     <row r="133" spans="1:4" ht="30" customHeight="1">
       <c r="A133" s="1" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B133" s="1" t="s">
         <v>21</v>
       </c>
       <c r="C133" s="1" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="D133" s="1" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
     </row>
     <row r="134" spans="1:4" ht="30" customHeight="1">
       <c r="A134" s="1" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="B134" s="1" t="s">
         <v>21</v>
       </c>
       <c r="C134" s="1" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="D134" s="1" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
     </row>
     <row r="135" spans="1:4" ht="30" customHeight="1">
       <c r="A135" s="1" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="B135" s="1" t="s">
         <v>22</v>
@@ -2738,7 +2736,7 @@
     </row>
     <row r="136" spans="1:4" ht="30" customHeight="1">
       <c r="A136" s="1" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="B136" s="1" t="s">
         <v>22</v>
@@ -2748,147 +2746,147 @@
     </row>
     <row r="137" spans="1:4" ht="30" customHeight="1">
       <c r="A137" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B137" s="1" t="s">
         <v>20</v>
       </c>
       <c r="C137" s="1" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="D137" s="1" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
     </row>
     <row r="138" spans="1:4" ht="30" customHeight="1">
       <c r="A138" s="1" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B138" s="1" t="s">
         <v>20</v>
       </c>
       <c r="C138" s="1" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="D138" s="1" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
     </row>
     <row r="139" spans="1:4" ht="30" customHeight="1">
       <c r="A139" s="1" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="B139" s="1" t="s">
         <v>20</v>
       </c>
       <c r="C139" s="1" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="D139" s="1" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
     </row>
     <row r="140" spans="1:4" ht="30" customHeight="1">
       <c r="A140" s="1" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="B140" s="1" t="s">
         <v>20</v>
       </c>
       <c r="C140" s="1" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="D140" s="1" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
     </row>
     <row r="141" spans="1:4" ht="30" customHeight="1">
       <c r="A141" s="1" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="B141" s="1" t="s">
         <v>20</v>
       </c>
       <c r="C141" s="1" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="D141" s="1" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
     </row>
     <row r="142" spans="1:4" ht="30" customHeight="1">
       <c r="A142" s="1" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="B142" s="1" t="s">
         <v>20</v>
       </c>
       <c r="C142" s="1" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="D142" s="1" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
     </row>
     <row r="143" spans="1:4" ht="30" customHeight="1">
       <c r="A143" s="1" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="B143" s="1" t="s">
         <v>21</v>
       </c>
       <c r="C143" s="1" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="D143" s="1" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
     </row>
     <row r="144" spans="1:4" ht="30" customHeight="1">
       <c r="A144" s="1" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B144" s="1" t="s">
         <v>21</v>
       </c>
       <c r="C144" s="1" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="D144" s="1" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
     </row>
     <row r="145" spans="1:4" ht="30" customHeight="1">
       <c r="A145" s="1" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="B145" s="1" t="s">
         <v>21</v>
       </c>
       <c r="C145" s="1" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="D145" s="1" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
     </row>
     <row r="146" spans="1:4" ht="30" customHeight="1">
       <c r="A146" s="1" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="B146" s="1" t="s">
         <v>21</v>
       </c>
       <c r="C146" s="1" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="D146" s="1" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
     </row>
     <row r="147" spans="1:4" ht="30" customHeight="1">
       <c r="A147" s="1" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="B147" s="1" t="s">
         <v>22</v>
@@ -2898,7 +2896,7 @@
     </row>
     <row r="148" spans="1:4" ht="30" customHeight="1">
       <c r="A148" s="1" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="B148" s="1" t="s">
         <v>22</v>
@@ -2908,7 +2906,7 @@
     </row>
     <row r="149" spans="1:4" ht="30" customHeight="1">
       <c r="A149" s="1" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="B149" s="1" t="s">
         <v>22</v>
@@ -2918,7 +2916,7 @@
     </row>
     <row r="150" spans="1:4" ht="30" customHeight="1">
       <c r="A150" s="1" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="B150" s="1" t="s">
         <v>22</v>
@@ -2928,49 +2926,45 @@
     </row>
     <row r="151" spans="1:4" ht="30" customHeight="1">
       <c r="A151" s="1" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="B151" s="1" t="s">
         <v>21</v>
       </c>
       <c r="C151" s="1" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="D151" s="1" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
     </row>
     <row r="152" spans="1:4" ht="30" customHeight="1">
       <c r="A152" s="1" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="B152" s="1" t="s">
         <v>21</v>
       </c>
       <c r="C152" s="1" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="D152" s="1" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
     </row>
     <row r="153" spans="1:4" ht="30" customHeight="1">
       <c r="A153" s="1" t="s">
-        <v>193</v>
+        <v>189</v>
       </c>
       <c r="B153" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="C153" s="1" t="s">
-        <v>210</v>
-      </c>
-      <c r="D153" s="1" t="s">
-        <v>225</v>
-      </c>
+        <v>22</v>
+      </c>
+      <c r="C153" s="1"/>
+      <c r="D153" s="1"/>
     </row>
     <row r="154" spans="1:4" ht="30" customHeight="1">
       <c r="A154" s="1" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="B154" s="1" t="s">
         <v>22</v>
@@ -2980,7 +2974,7 @@
     </row>
     <row r="155" spans="1:4" ht="30" customHeight="1">
       <c r="A155" s="1" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="B155" s="1" t="s">
         <v>22</v>
@@ -2990,13 +2984,17 @@
     </row>
     <row r="156" spans="1:4" ht="30" customHeight="1">
       <c r="A156" s="1" t="s">
-        <v>190</v>
+        <v>148</v>
       </c>
       <c r="B156" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="C156" s="1"/>
-      <c r="D156" s="1"/>
+        <v>21</v>
+      </c>
+      <c r="C156" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="D156" s="1" t="s">
+        <v>222</v>
+      </c>
     </row>
     <row r="157" spans="1:4" ht="30" customHeight="1">
       <c r="A157" s="1" t="s">
@@ -3006,38 +3004,38 @@
         <v>21</v>
       </c>
       <c r="C157" s="1" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="D157" s="1" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
     </row>
     <row r="158" spans="1:4" ht="30" customHeight="1">
       <c r="A158" s="1" t="s">
-        <v>150</v>
+        <v>187</v>
       </c>
       <c r="B158" s="1" t="s">
         <v>21</v>
       </c>
       <c r="C158" s="1" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="D158" s="1" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
     </row>
     <row r="159" spans="1:4" ht="30" customHeight="1">
       <c r="A159" s="1" t="s">
-        <v>189</v>
+        <v>150</v>
       </c>
       <c r="B159" s="1" t="s">
-        <v>21</v>
+        <v>227</v>
       </c>
       <c r="C159" s="1" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="D159" s="1" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
     </row>
     <row r="160" spans="1:4" ht="30" customHeight="1">
@@ -3045,125 +3043,125 @@
         <v>151</v>
       </c>
       <c r="B160" s="1" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="C160" s="1" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="D160" s="1" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
     </row>
     <row r="161" spans="1:4" ht="30" customHeight="1">
       <c r="A161" s="1" t="s">
-        <v>152</v>
+        <v>186</v>
       </c>
       <c r="B161" s="1" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="C161" s="1" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="D161" s="1" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
     </row>
     <row r="162" spans="1:4" ht="30" customHeight="1">
       <c r="A162" s="1" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="B162" s="1" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="C162" s="1" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="D162" s="1" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
     </row>
     <row r="163" spans="1:4" ht="30" customHeight="1">
       <c r="A163" s="1" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="B163" s="1" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="C163" s="1" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="D163" s="1" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
     </row>
     <row r="164" spans="1:4" ht="30" customHeight="1">
       <c r="A164" s="1" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="B164" s="1" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="C164" s="1" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="D164" s="1" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
     </row>
     <row r="165" spans="1:4" ht="30" customHeight="1">
       <c r="A165" s="1" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="B165" s="1" t="s">
-        <v>230</v>
+        <v>21</v>
       </c>
       <c r="C165" s="1" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="D165" s="1" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
     </row>
     <row r="166" spans="1:4" ht="30" customHeight="1">
       <c r="A166" s="1" t="s">
-        <v>184</v>
+        <v>152</v>
       </c>
       <c r="B166" s="1" t="s">
         <v>21</v>
       </c>
       <c r="C166" s="1" t="s">
-        <v>209</v>
+        <v>214</v>
       </c>
       <c r="D166" s="1" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
     </row>
     <row r="167" spans="1:4" ht="30" customHeight="1">
       <c r="A167" s="1" t="s">
-        <v>153</v>
+        <v>181</v>
       </c>
       <c r="B167" s="1" t="s">
         <v>21</v>
       </c>
       <c r="C167" s="1" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="D167" s="1" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
     </row>
     <row r="168" spans="1:4" ht="30" customHeight="1">
       <c r="A168" s="1" t="s">
-        <v>183</v>
+        <v>153</v>
       </c>
       <c r="B168" s="1" t="s">
         <v>21</v>
       </c>
       <c r="C168" s="1" t="s">
-        <v>218</v>
+        <v>207</v>
       </c>
       <c r="D168" s="1" t="s">
-        <v>229</v>
+        <v>222</v>
       </c>
     </row>
     <row r="169" spans="1:4" ht="30" customHeight="1">
@@ -3174,59 +3172,59 @@
         <v>21</v>
       </c>
       <c r="C169" s="1" t="s">
-        <v>210</v>
+        <v>206</v>
       </c>
       <c r="D169" s="1" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
     </row>
     <row r="170" spans="1:4" ht="30" customHeight="1">
       <c r="A170" s="1" t="s">
-        <v>155</v>
+        <v>180</v>
       </c>
       <c r="B170" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="C170" s="1" t="s">
-        <v>209</v>
-      </c>
-      <c r="D170" s="1" t="s">
-        <v>225</v>
-      </c>
+        <v>22</v>
+      </c>
+      <c r="C170" s="1"/>
+      <c r="D170" s="1"/>
     </row>
     <row r="171" spans="1:4" ht="30" customHeight="1">
       <c r="A171" s="1" t="s">
-        <v>182</v>
+        <v>155</v>
       </c>
       <c r="B171" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="C171" s="1"/>
-      <c r="D171" s="1"/>
+        <v>21</v>
+      </c>
+      <c r="C171" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="D171" s="1" t="s">
+        <v>222</v>
+      </c>
     </row>
     <row r="172" spans="1:4" ht="30" customHeight="1">
       <c r="A172" s="1" t="s">
-        <v>156</v>
+        <v>179</v>
       </c>
       <c r="B172" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="C172" s="1" t="s">
-        <v>210</v>
-      </c>
-      <c r="D172" s="1" t="s">
-        <v>225</v>
-      </c>
+        <v>22</v>
+      </c>
+      <c r="C172" s="1"/>
+      <c r="D172" s="1"/>
     </row>
     <row r="173" spans="1:4" ht="30" customHeight="1">
       <c r="A173" s="1" t="s">
-        <v>181</v>
+        <v>156</v>
       </c>
       <c r="B173" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="C173" s="1"/>
-      <c r="D173" s="1"/>
+        <v>21</v>
+      </c>
+      <c r="C173" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="D173" s="1" t="s">
+        <v>222</v>
+      </c>
     </row>
     <row r="174" spans="1:4" ht="30" customHeight="1">
       <c r="A174" s="1" t="s">
@@ -3236,29 +3234,25 @@
         <v>21</v>
       </c>
       <c r="C174" s="1" t="s">
-        <v>210</v>
+        <v>216</v>
       </c>
       <c r="D174" s="1" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
     </row>
     <row r="175" spans="1:4" ht="30" customHeight="1">
       <c r="A175" s="1" t="s">
-        <v>158</v>
+        <v>178</v>
       </c>
       <c r="B175" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="C175" s="1" t="s">
-        <v>219</v>
-      </c>
-      <c r="D175" s="1" t="s">
-        <v>225</v>
-      </c>
+        <v>22</v>
+      </c>
+      <c r="C175" s="1"/>
+      <c r="D175" s="1"/>
     </row>
     <row r="176" spans="1:4" ht="30" customHeight="1">
       <c r="A176" s="1" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="B176" s="1" t="s">
         <v>22</v>
@@ -3268,31 +3262,31 @@
     </row>
     <row r="177" spans="1:4" ht="30" customHeight="1">
       <c r="A177" s="1" t="s">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="B177" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="C177" s="1"/>
-      <c r="D177" s="1"/>
+        <v>21</v>
+      </c>
+      <c r="C177" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="D177" s="1" t="s">
+        <v>222</v>
+      </c>
     </row>
     <row r="178" spans="1:4" ht="30" customHeight="1">
       <c r="A178" s="1" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="B178" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="C178" s="1" t="s">
-        <v>209</v>
-      </c>
-      <c r="D178" s="1" t="s">
-        <v>225</v>
-      </c>
+        <v>22</v>
+      </c>
+      <c r="C178" s="1"/>
+      <c r="D178" s="1"/>
     </row>
     <row r="179" spans="1:4" ht="30" customHeight="1">
       <c r="A179" s="1" t="s">
-        <v>178</v>
+        <v>158</v>
       </c>
       <c r="B179" s="1" t="s">
         <v>22</v>
@@ -3300,18 +3294,8 @@
       <c r="C179" s="1"/>
       <c r="D179" s="1"/>
     </row>
-    <row r="180" spans="1:4" ht="30" customHeight="1">
-      <c r="A180" s="1" t="s">
-        <v>159</v>
-      </c>
-      <c r="B180" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="C180" s="1"/>
-      <c r="D180" s="1"/>
-    </row>
   </sheetData>
-  <autoFilter ref="B1:B180">
+  <autoFilter ref="B1:B179">
     <filterColumn colId="0"/>
   </autoFilter>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -3339,10 +3323,10 @@
         <v>19</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
     </row>
     <row r="2" spans="1:4" ht="20.100000000000001" customHeight="1">
@@ -3353,10 +3337,10 @@
         <v>21</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
     </row>
     <row r="3" spans="1:4" hidden="1">
@@ -3375,10 +3359,10 @@
         <v>21</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="20.100000000000001" customHeight="1">
@@ -3389,10 +3373,10 @@
         <v>21</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
     </row>
     <row r="6" spans="1:4" hidden="1">
@@ -3411,10 +3395,10 @@
         <v>21</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
     </row>
   </sheetData>
@@ -3501,7 +3485,7 @@
         <v>17</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
     </row>
     <row r="2" spans="1:4" ht="20.100000000000001" customHeight="1">
@@ -3509,13 +3493,13 @@
         <v>7</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
     </row>
     <row r="3" spans="1:4" ht="20.100000000000001" hidden="1" customHeight="1">
@@ -3523,11 +3507,11 @@
         <v>8</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="4" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
     </row>
     <row r="4" spans="1:4" ht="20.100000000000001" hidden="1" customHeight="1">
@@ -3535,11 +3519,11 @@
         <v>9</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
       <c r="C4" s="1"/>
       <c r="D4" s="4" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="20.100000000000001" hidden="1" customHeight="1">
@@ -3547,11 +3531,11 @@
         <v>10</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
       <c r="C5" s="1"/>
       <c r="D5" s="4" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="20.100000000000001" hidden="1" customHeight="1">
@@ -3559,23 +3543,23 @@
         <v>11</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
       <c r="C6" s="1"/>
       <c r="D6" s="4" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="36.75" hidden="1" customHeight="1">
       <c r="A7" s="1" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="C7" s="1"/>
       <c r="D7" s="4" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="20.100000000000001" hidden="1" customHeight="1">
@@ -3583,11 +3567,11 @@
         <v>12</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="C8" s="1"/>
       <c r="D8" s="4" t="s">
-        <v>241</v>
+        <v>238</v>
       </c>
     </row>
     <row r="9" spans="1:4" ht="20.100000000000001" hidden="1" customHeight="1">
@@ -3595,23 +3579,23 @@
         <v>13</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="C9" s="1"/>
       <c r="D9" s="4" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
     </row>
     <row r="10" spans="1:4" ht="26.25" hidden="1" customHeight="1">
       <c r="A10" s="1" t="s">
-        <v>243</v>
+        <v>240</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="C10" s="1"/>
       <c r="D10" s="4" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
     </row>
     <row r="11" spans="1:4" ht="20.100000000000001" customHeight="1">
@@ -3619,13 +3603,13 @@
         <v>14</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>245</v>
+        <v>242</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
     </row>
     <row r="12" spans="1:4" ht="20.100000000000001" hidden="1" customHeight="1">
@@ -3633,23 +3617,23 @@
         <v>15</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="C12" s="1"/>
       <c r="D12" s="4" t="s">
-        <v>246</v>
+        <v>243</v>
       </c>
     </row>
     <row r="13" spans="1:4" ht="20.100000000000001" hidden="1" customHeight="1">
       <c r="A13" s="1" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="C13" s="1"/>
       <c r="D13" s="4" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
     </row>
     <row r="14" spans="1:4" ht="20.100000000000001" hidden="1" customHeight="1">
@@ -3657,11 +3641,11 @@
         <v>16</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="C14" s="1"/>
       <c r="D14" s="4" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
     </row>
     <row r="15" spans="1:4" ht="20.100000000000001" customHeight="1">
@@ -3669,13 +3653,13 @@
         <v>29</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>245</v>
+        <v>242</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="D15" s="4" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
     </row>
   </sheetData>
@@ -3690,4 +3674,15 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="13.5"/>
+  <sheetData/>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
 </file>
--- a/internal_doc/05.测试设计/story/mysql连接器/5.7.24测试用例差别.xlsx
+++ b/internal_doc/05.测试设计/story/mysql连接器/5.7.24测试用例差别.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="565" uniqueCount="250">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="565" uniqueCount="251">
   <si>
     <t>r</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -130,394 +130,748 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
+    <t>bigint.result</t>
+  </si>
+  <si>
+    <t>cache_innodb.result</t>
+  </si>
+  <si>
+    <t>check.result</t>
+  </si>
+  <si>
+    <t>concurrent_innodb_unsafelog.result</t>
+  </si>
+  <si>
+    <t>connect.result</t>
+  </si>
+  <si>
+    <t>date_formats.result</t>
+  </si>
+  <si>
+    <t>ddl_i18n_utf8.result</t>
+  </si>
+  <si>
+    <t>derived.result</t>
+  </si>
+  <si>
+    <t>flush_read_lock.result</t>
+  </si>
+  <si>
+    <t>fulltext.result</t>
+  </si>
+  <si>
+    <t>func_gconcat.result</t>
+  </si>
+  <si>
+    <t>func_group.result</t>
+  </si>
+  <si>
+    <t>func_in_icp.result</t>
+  </si>
+  <si>
+    <t>func_in_icp_mrr.result</t>
+  </si>
+  <si>
+    <t>func_in_mrr.result</t>
+  </si>
+  <si>
+    <t>func_in_mrr_cost.result</t>
+  </si>
+  <si>
+    <t>func_in_none.result</t>
+  </si>
+  <si>
+    <t>func_math.result</t>
+  </si>
+  <si>
+    <t>gis.result</t>
+  </si>
+  <si>
+    <t>gis-precise.result</t>
+  </si>
+  <si>
+    <t>gis-rtree.result</t>
+  </si>
+  <si>
+    <t>grant.result</t>
+  </si>
+  <si>
+    <t>grant_alter_user_qa.result</t>
+  </si>
+  <si>
+    <t>grant_cache.result</t>
+  </si>
+  <si>
+    <t>grant_debug.result</t>
+  </si>
+  <si>
+    <t>grant_user_lock_qa.result</t>
+  </si>
+  <si>
+    <t>grant2.result</t>
+  </si>
+  <si>
+    <t>group_by.result</t>
+  </si>
+  <si>
+    <t>group_min_max.result</t>
+  </si>
+  <si>
+    <t>group_min_max_innodb.result</t>
+  </si>
+  <si>
+    <t>index_merge_intersect_dml.result</t>
+  </si>
+  <si>
+    <t>information_schema.result</t>
+  </si>
+  <si>
+    <t>init_connect.result</t>
+  </si>
+  <si>
+    <t>initialize-bug20350099.result</t>
+  </si>
+  <si>
+    <t>initialize-sha256.result</t>
+  </si>
+  <si>
+    <t>innodb_explain_json_non_select_all.result</t>
+  </si>
+  <si>
+    <t>innodb_explain_json_non_select_none.result</t>
+  </si>
+  <si>
+    <t>innodb_explain_non_select_all.result</t>
+  </si>
+  <si>
+    <t>innodb_explain_non_select_none.result</t>
+  </si>
+  <si>
+    <t>innodb_mrr_all.result</t>
+  </si>
+  <si>
+    <t>innodb_mrr_cost.result</t>
+  </si>
+  <si>
+    <t>innodb_mrr_cost_all.result</t>
+  </si>
+  <si>
+    <t>innodb_mrr_cost_icp.result</t>
+  </si>
+  <si>
+    <t>innodb_mrr_icp.result</t>
+  </si>
+  <si>
+    <t>innodb_mrr_none.result</t>
+  </si>
+  <si>
+    <t>join_outer_bka.result</t>
+  </si>
+  <si>
+    <t>join_outer_bka_nixbnl.result</t>
+  </si>
+  <si>
+    <t>locking_service.result</t>
+  </si>
+  <si>
+    <t>max_statement_time.result</t>
+  </si>
+  <si>
+    <t>mdl_sync.result</t>
+  </si>
+  <si>
+    <t>mix2_myisam.result</t>
+  </si>
+  <si>
+    <t>multi_update.result</t>
+  </si>
+  <si>
+    <t>myisam_explain_json_non_select_all.result</t>
+  </si>
+  <si>
+    <t>myisam_explain_json_non_select_none.result</t>
+  </si>
+  <si>
+    <t>myisam_explain_non_select_all.result</t>
+  </si>
+  <si>
+    <t>myisam_explain_non_select_none.result</t>
+  </si>
+  <si>
+    <t>myisam-blob.result</t>
+  </si>
+  <si>
+    <t>mysql_not_windows.result</t>
+  </si>
+  <si>
+    <t>mysql_upgrade.result</t>
+  </si>
+  <si>
+    <t>mysqladmin.result</t>
+  </si>
+  <si>
+    <t>mysqlcheck.result</t>
+  </si>
+  <si>
+    <t>mysqld--help-notwin.result</t>
+  </si>
+  <si>
+    <t>mysqld--help-win.result</t>
+  </si>
+  <si>
+    <t>mysqldump.result</t>
+  </si>
+  <si>
+    <t>mysqlpump.result</t>
+  </si>
+  <si>
+    <t>mysqlpump_basic.result</t>
+  </si>
+  <si>
+    <t>mysqltest.result</t>
+  </si>
+  <si>
+    <t>olap.result</t>
+  </si>
+  <si>
+    <t>partition.result</t>
+  </si>
+  <si>
+    <t>partition_cache.result</t>
+  </si>
+  <si>
+    <t>partition_deprecation.result</t>
+  </si>
+  <si>
+    <t>partition_hash.result</t>
+  </si>
+  <si>
+    <t>partition_innodb.result</t>
+  </si>
+  <si>
+    <t>partition_innodb_tablespace.result</t>
+  </si>
+  <si>
+    <t>partition_list.result</t>
+  </si>
+  <si>
+    <t>partition_locking.result</t>
+  </si>
+  <si>
+    <t>partition_pruning.result</t>
+  </si>
+  <si>
+    <t>partition_range.result</t>
+  </si>
+  <si>
+    <t>plugin_auth.result</t>
+  </si>
+  <si>
+    <t>plugin_auth_qa.result</t>
+  </si>
+  <si>
+    <t>plugin_auth_qa_1.result</t>
+  </si>
+  <si>
+    <t>plugin_auth_qa_2.result</t>
+  </si>
+  <si>
+    <t>plugin_auth_sha256.result</t>
+  </si>
+  <si>
+    <t>plugin_auth_sha256_2.result</t>
+  </si>
+  <si>
+    <t>plugin_auth_sha256_server_default.result</t>
+  </si>
+  <si>
+    <t>plugin_auth_sha256_server_default_tls.result</t>
+  </si>
+  <si>
+    <t>ps_1general.result</t>
+  </si>
+  <si>
+    <t>query_cache_28249.result</t>
+  </si>
+  <si>
+    <t>query_cache_debug.result</t>
+  </si>
+  <si>
+    <t>query_cache_disabled.result</t>
+  </si>
+  <si>
+    <t>query_cache_merge.result</t>
+  </si>
+  <si>
+    <t>query_cache_notembedded.result</t>
+  </si>
+  <si>
+    <t>query_cache_ps_no_prot.result</t>
+  </si>
+  <si>
+    <t>query_cache_size_functionality.result</t>
+  </si>
+  <si>
+    <t>query_cache_type_functionality.result</t>
+  </si>
+  <si>
+    <t>query_cache_with_views.result</t>
+  </si>
+  <si>
+    <t>range_all.result</t>
+  </si>
+  <si>
+    <t>range_icp.result</t>
+  </si>
+  <si>
+    <t>range_icp_mrr.result</t>
+  </si>
+  <si>
+    <t>range_mrr.result</t>
+  </si>
+  <si>
+    <t>range_mrr_cost.result</t>
+  </si>
+  <si>
+    <t>range_none.result</t>
+  </si>
+  <si>
+    <t>select_all.result</t>
+  </si>
+  <si>
+    <t>select_all_bka.result</t>
+  </si>
+  <si>
+    <t>select_all_bka_nixbnl.result</t>
+  </si>
+  <si>
+    <t>select_icp_mrr.result</t>
+  </si>
+  <si>
+    <t>select_icp_mrr_bka.result</t>
+  </si>
+  <si>
+    <t>select_icp_mrr_bka_nixbnl.result</t>
+  </si>
+  <si>
+    <t>select_none.result</t>
+  </si>
+  <si>
+    <t>select_none_bka.result</t>
+  </si>
+  <si>
+    <t>select_none_bka_nixbnl.result</t>
+  </si>
+  <si>
+    <t>select_safe.result</t>
+  </si>
+  <si>
+    <t>session_tracker.result</t>
+  </si>
+  <si>
+    <t>show_check.result</t>
+  </si>
+  <si>
+    <t>signal_demo1.result</t>
+  </si>
+  <si>
+    <t>sp.result</t>
+  </si>
+  <si>
+    <t>subquery_all.result</t>
+  </si>
+  <si>
+    <t>subquery_all_bka.result</t>
+  </si>
+  <si>
+    <t>subquery_nomat_nosj.result</t>
+  </si>
+  <si>
+    <t>subquery_nomat_nosj_bka.result</t>
+  </si>
+  <si>
+    <t>trigger.result</t>
+  </si>
+  <si>
+    <t>type_newdecimal.result</t>
+  </si>
+  <si>
+    <t>type_timestamp.result</t>
+  </si>
+  <si>
+    <t>type_year.result</t>
+  </si>
+  <si>
+    <t>union.result</t>
+  </si>
+  <si>
+    <t>update.result</t>
+  </si>
+  <si>
+    <t>xa.result</t>
+  </si>
+  <si>
+    <t>ansi.result</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>commit.result</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>concurrent_innodb_safelog.result</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ddl_i18n_koi8r.result</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>deprecate_eof.result</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>events_bugs.result</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>func_misc.result</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ignore_strict.result</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>index_merge_innodb.result</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>initialize.result</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>innodb_mrr.result</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>innodb_mysql_lock2.result</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>innodb_mysql_sync.result</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>key.result</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>loaddata.result</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>varbinary.result</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>variables.result</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>user_var.result</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>user_if_exists.result</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>udf.result</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>type_timestamp_explicit.result</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>trigger_wl3253.result</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>trans_read_only.result</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>subquery_none_bka_nixbnl.result</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>subquery_none_bka.result</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>subquery_none.result</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>subquery_nomat_nosj_bka_nixbnl.result</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>subquery_all_bka_nixbnl.result</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>status.result</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sql_mode.result</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ssl_crl.result</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sp_notembedded.result</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>session_tracker_trx_state.result</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>reset_connection.result</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>range_with_memory_limit.result</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>query_cache.result</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ps.result</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>parser.result</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>odbc.result</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>opt_hints.result</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>log_tables.result</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>lowercase_table_qcache.result</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>mdl_tablespace.result</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>m_i_db.result</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>备注</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>测试步骤相同，5.7.24多告警信息</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>测试文件末尾，5.7.24多了测试步骤</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>部分测试步骤预期结果有调整，同时测试文件默认，5.7.24多了测试步骤</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>步骤步骤相同，5.7.24多告警信息及预期结果</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>测试文件末尾，5.7.24多了测试步骤，修改了预期结果</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>测试文件末尾，5.7.24多了测试步骤，修改了预期结果的记录顺序</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>测试步骤相同，5.7.24多插入了一条记录</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>测试文件末尾，5.7.24多了测试步骤，同时多了告警信息</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>测试文件末尾，5.7.24多了测试步骤，同时多了告警信息，修改了预期结果</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>测试步骤相同，5.7.24修改了预期结果</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>测试步骤相同，5.7.24修改了ERROR信息</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>备注</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>修改了预期结果</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>测试文件末尾，5.7.24多了测试步骤</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>修改了测试步骤，测试文件末尾，5.7.24多了测试步骤</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>是否已修改</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>已修改</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>多了一个explain测试步骤，修改了一条执行语句</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>func_in_all.result</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>不需修改用例</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>不需修改，修改了预期结果的步骤由于不支持已屏蔽</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>是</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>否</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>备注</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>验证innodb数据导入功能，不对接</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>否</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>验证upgrade功能，不对接</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>验证dump功能，不对接</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>验证pump功能，不对接</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>no_engine_substitution.test</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>验证no_engine_substitution模式(no_engine_substitution-master.opt)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>验证show_processlist，不对接</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>需要debug版本，暂不对接</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ssl_verify_identity.test</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>验证ssl_mode=verify_identity，暂不对接（ssl_verify_identity-master.opt）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>是</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>transaction_read_only.test</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>设置tx_read_only为on、off、default时，查询session上的该变量，暂不对接（transaction_read_only-master.opt）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>验证mysql的dump、import等工具的功能，暂时不对接（utility_warnings-master.opt）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>已修改，row_format只支持fixed格式</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>delete.result</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>join_outer.result</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>测试文件末尾，5.7.24多了测试步骤，新增了parser-master.opt文件</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
     <t>alter_table.result</t>
-  </si>
-  <si>
-    <t>bigint.result</t>
-  </si>
-  <si>
-    <t>cache_innodb.result</t>
-  </si>
-  <si>
-    <t>check.result</t>
-  </si>
-  <si>
-    <t>concurrent_innodb_unsafelog.result</t>
-  </si>
-  <si>
-    <t>connect.result</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>create.result</t>
-  </si>
-  <si>
-    <t>date_formats.result</t>
-  </si>
-  <si>
-    <t>ddl_i18n_utf8.result</t>
-  </si>
-  <si>
-    <t>derived.result</t>
-  </si>
-  <si>
-    <t>flush_read_lock.result</t>
-  </si>
-  <si>
-    <t>fulltext.result</t>
-  </si>
-  <si>
-    <t>func_gconcat.result</t>
-  </si>
-  <si>
-    <t>func_group.result</t>
-  </si>
-  <si>
-    <t>func_in_icp.result</t>
-  </si>
-  <si>
-    <t>func_in_icp_mrr.result</t>
-  </si>
-  <si>
-    <t>func_in_mrr.result</t>
-  </si>
-  <si>
-    <t>func_in_mrr_cost.result</t>
-  </si>
-  <si>
-    <t>func_in_none.result</t>
-  </si>
-  <si>
-    <t>func_math.result</t>
-  </si>
-  <si>
-    <t>gis.result</t>
-  </si>
-  <si>
-    <t>gis-precise.result</t>
-  </si>
-  <si>
-    <t>gis-rtree.result</t>
-  </si>
-  <si>
-    <t>grant.result</t>
-  </si>
-  <si>
-    <t>grant_alter_user_qa.result</t>
-  </si>
-  <si>
-    <t>grant_cache.result</t>
-  </si>
-  <si>
-    <t>grant_debug.result</t>
-  </si>
-  <si>
-    <t>grant_user_lock_qa.result</t>
-  </si>
-  <si>
-    <t>grant2.result</t>
-  </si>
-  <si>
-    <t>group_by.result</t>
-  </si>
-  <si>
-    <t>group_min_max.result</t>
-  </si>
-  <si>
-    <t>group_min_max_innodb.result</t>
-  </si>
-  <si>
-    <t>index_merge_intersect_dml.result</t>
-  </si>
-  <si>
-    <t>information_schema.result</t>
-  </si>
-  <si>
-    <t>init_connect.result</t>
-  </si>
-  <si>
-    <t>initialize-bug20350099.result</t>
-  </si>
-  <si>
-    <t>initialize-sha256.result</t>
-  </si>
-  <si>
-    <t>innodb_explain_json_non_select_all.result</t>
-  </si>
-  <si>
-    <t>innodb_explain_json_non_select_none.result</t>
-  </si>
-  <si>
-    <t>innodb_explain_non_select_all.result</t>
-  </si>
-  <si>
-    <t>innodb_explain_non_select_none.result</t>
-  </si>
-  <si>
-    <t>innodb_mrr_all.result</t>
-  </si>
-  <si>
-    <t>innodb_mrr_cost.result</t>
-  </si>
-  <si>
-    <t>innodb_mrr_cost_all.result</t>
-  </si>
-  <si>
-    <t>innodb_mrr_cost_icp.result</t>
-  </si>
-  <si>
-    <t>innodb_mrr_icp.result</t>
-  </si>
-  <si>
-    <t>innodb_mrr_none.result</t>
-  </si>
-  <si>
-    <t>join_outer_bka.result</t>
-  </si>
-  <si>
-    <t>join_outer_bka_nixbnl.result</t>
-  </si>
-  <si>
-    <t>locking_service.result</t>
-  </si>
-  <si>
-    <t>max_statement_time.result</t>
-  </si>
-  <si>
-    <t>mdl_sync.result</t>
-  </si>
-  <si>
-    <t>mix2_myisam.result</t>
-  </si>
-  <si>
-    <t>multi_update.result</t>
-  </si>
-  <si>
-    <t>myisam_explain_json_non_select_all.result</t>
-  </si>
-  <si>
-    <t>myisam_explain_json_non_select_none.result</t>
-  </si>
-  <si>
-    <t>myisam_explain_non_select_all.result</t>
-  </si>
-  <si>
-    <t>myisam_explain_non_select_none.result</t>
-  </si>
-  <si>
-    <t>myisam-blob.result</t>
-  </si>
-  <si>
-    <t>mysql_not_windows.result</t>
-  </si>
-  <si>
-    <t>mysql_upgrade.result</t>
-  </si>
-  <si>
-    <t>mysqladmin.result</t>
-  </si>
-  <si>
-    <t>mysqlcheck.result</t>
-  </si>
-  <si>
-    <t>mysqld--help-notwin.result</t>
-  </si>
-  <si>
-    <t>mysqld--help-win.result</t>
-  </si>
-  <si>
-    <t>mysqldump.result</t>
-  </si>
-  <si>
-    <t>mysqlpump.result</t>
-  </si>
-  <si>
-    <t>mysqlpump_basic.result</t>
-  </si>
-  <si>
-    <t>mysqltest.result</t>
-  </si>
-  <si>
-    <t>olap.result</t>
-  </si>
-  <si>
-    <t>partition.result</t>
-  </si>
-  <si>
-    <t>partition_cache.result</t>
-  </si>
-  <si>
-    <t>partition_deprecation.result</t>
-  </si>
-  <si>
-    <t>partition_hash.result</t>
-  </si>
-  <si>
-    <t>partition_innodb.result</t>
-  </si>
-  <si>
-    <t>partition_innodb_tablespace.result</t>
-  </si>
-  <si>
-    <t>partition_list.result</t>
-  </si>
-  <si>
-    <t>partition_locking.result</t>
-  </si>
-  <si>
-    <t>partition_pruning.result</t>
-  </si>
-  <si>
-    <t>partition_range.result</t>
-  </si>
-  <si>
-    <t>plugin_auth.result</t>
-  </si>
-  <si>
-    <t>plugin_auth_qa.result</t>
-  </si>
-  <si>
-    <t>plugin_auth_qa_1.result</t>
-  </si>
-  <si>
-    <t>plugin_auth_qa_2.result</t>
-  </si>
-  <si>
-    <t>plugin_auth_sha256.result</t>
-  </si>
-  <si>
-    <t>plugin_auth_sha256_2.result</t>
-  </si>
-  <si>
-    <t>plugin_auth_sha256_server_default.result</t>
-  </si>
-  <si>
-    <t>plugin_auth_sha256_server_default_tls.result</t>
-  </si>
-  <si>
-    <t>ps_1general.result</t>
-  </si>
-  <si>
-    <t>query_cache_28249.result</t>
-  </si>
-  <si>
-    <t>query_cache_debug.result</t>
-  </si>
-  <si>
-    <t>query_cache_disabled.result</t>
-  </si>
-  <si>
-    <t>query_cache_merge.result</t>
-  </si>
-  <si>
-    <t>query_cache_notembedded.result</t>
-  </si>
-  <si>
-    <t>query_cache_ps_no_prot.result</t>
-  </si>
-  <si>
-    <t>query_cache_size_functionality.result</t>
-  </si>
-  <si>
-    <t>query_cache_type_functionality.result</t>
-  </si>
-  <si>
-    <t>query_cache_with_views.result</t>
-  </si>
-  <si>
-    <t>range_all.result</t>
-  </si>
-  <si>
-    <t>range_icp.result</t>
-  </si>
-  <si>
-    <t>range_icp_mrr.result</t>
-  </si>
-  <si>
-    <t>range_mrr.result</t>
-  </si>
-  <si>
-    <t>range_mrr_cost.result</t>
-  </si>
-  <si>
-    <t>range_none.result</t>
-  </si>
-  <si>
-    <t>select_all.result</t>
-  </si>
-  <si>
-    <t>select_all_bka.result</t>
-  </si>
-  <si>
-    <t>select_all_bka_nixbnl.result</t>
-  </si>
-  <si>
-    <t>select_icp_mrr.result</t>
-  </si>
-  <si>
-    <t>select_icp_mrr_bka.result</t>
-  </si>
-  <si>
-    <t>select_icp_mrr_bka_nixbnl.result</t>
-  </si>
-  <si>
-    <t>select_none.result</t>
-  </si>
-  <si>
-    <t>select_none_bka.result</t>
-  </si>
-  <si>
-    <t>select_none_bka_nixbnl.result</t>
-  </si>
-  <si>
-    <t>select_safe.result</t>
-  </si>
-  <si>
-    <t>session_tracker.result</t>
-  </si>
-  <si>
-    <t>show_check.result</t>
-  </si>
-  <si>
-    <t>signal_demo1.result</t>
-  </si>
-  <si>
-    <t>sp.result</t>
-  </si>
-  <si>
-    <t>subquery_all.result</t>
-  </si>
-  <si>
-    <t>subquery_all_bka.result</t>
-  </si>
-  <si>
-    <t>subquery_nomat_nosj.result</t>
-  </si>
-  <si>
-    <t>subquery_nomat_nosj_bka.result</t>
-  </si>
-  <si>
-    <t>trigger.result</t>
-  </si>
-  <si>
-    <t>type_newdecimal.result</t>
-  </si>
-  <si>
-    <t>type_timestamp.result</t>
-  </si>
-  <si>
-    <t>type_year.result</t>
-  </si>
-  <si>
-    <t>union.result</t>
-  </si>
-  <si>
-    <t>update.result</t>
-  </si>
-  <si>
-    <t>xa.result</t>
-  </si>
-  <si>
-    <t>ansi.result</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>测试文件末尾，5.7.24多了测试步骤</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -525,359 +879,11 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>commit.result</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>concurrent_innodb_safelog.result</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ddl_i18n_koi8r.result</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>deprecate_eof.result</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>events_bugs.result</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>func_misc.result</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ignore_strict.result</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>index_merge_innodb.result</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>initialize.result</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>innodb_mrr.result</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>innodb_mysql_lock2.result</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>innodb_mysql_sync.result</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>key.result</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>loaddata.result</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>varbinary.result</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>variables.result</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>user_var.result</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>user_if_exists.result</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>udf.result</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>type_timestamp_explicit.result</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>trigger_wl3253.result</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>trans_read_only.result</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>subquery_none_bka_nixbnl.result</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>subquery_none_bka.result</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>subquery_none.result</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>subquery_nomat_nosj_bka_nixbnl.result</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>subquery_all_bka_nixbnl.result</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>status.result</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>sql_mode.result</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ssl_crl.result</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>sp_notembedded.result</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>session_tracker_trx_state.result</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>reset_connection.result</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>range_with_memory_limit.result</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>query_cache.result</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ps.result</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>parser.result</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>odbc.result</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>opt_hints.result</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>log_tables.result</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>lowercase_table_qcache.result</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>metadata.result</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>mdl_tablespace.result</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>m_i_db.result</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>备注</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>测试步骤相同，5.7.24多告警信息</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>测试文件末尾，5.7.24多了测试步骤</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>部分测试步骤预期结果有调整，同时测试文件默认，5.7.24多了测试步骤</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>步骤步骤相同，5.7.24多告警信息及预期结果</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>测试文件末尾，5.7.24多了测试步骤，修改了预期结果</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>测试文件末尾，5.7.24多了测试步骤，修改了预期结果的记录顺序</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>测试步骤相同，5.7.24多插入了一条记录</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>测试文件末尾，5.7.24多了测试步骤，同时多了告警信息</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>测试文件末尾，5.7.24多了测试步骤，同时多了告警信息，修改了预期结果</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>测试步骤相同，5.7.24修改了预期结果</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>测试步骤相同，5.7.24修改了ERROR信息</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>备注</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>修改了预期结果</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>测试文件末尾，5.7.24多了测试步骤</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>修改了测试步骤，测试文件末尾，5.7.24多了测试步骤</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>是否已修改</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>已修改</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>多了一个explain测试步骤，修改了一条执行语句</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>func_in_all.result</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>不需修改用例</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>不需修改，修改了预期结果的步骤由于不支持已屏蔽</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>是</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>否</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>备注</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>验证innodb数据导入功能，不对接</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>否</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>验证upgrade功能，不对接</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>验证dump功能，不对接</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>验证pump功能，不对接</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>no_engine_substitution.test</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>验证no_engine_substitution模式(no_engine_substitution-master.opt)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>测试文件末尾，5.7.24多了测试步骤，新增了parser-master.opt文件</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>验证show_processlist，不对接</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>需要debug版本，暂不对接</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ssl_verify_identity.test</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>验证ssl_mode=verify_identity，暂不对接（ssl_verify_identity-master.opt）</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>是</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>事务隔离级别相关，暂不对接，后续需对接（transaction_isolation-master.opt）</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>transaction_read_only.test</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>设置tx_read_only为on、off、default时，查询session上的该变量，暂不对接（transaction_read_only-master.opt）</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>验证mysql的dump、import等工具的功能，暂时不对接（utility_warnings-master.opt）</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>已修改，row_format只支持fixed格式</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>delete.result</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>join_outer.result</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1260,15 +1266,15 @@
         <v>19</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>205</v>
+        <v>201</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>221</v>
+        <v>217</v>
       </c>
     </row>
     <row r="2" spans="1:4" ht="30" customHeight="1">
       <c r="A2" s="1" t="s">
-        <v>30</v>
+        <v>245</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>6</v>
@@ -1278,21 +1284,21 @@
     </row>
     <row r="3" spans="1:4" ht="30" customHeight="1">
       <c r="A3" s="1" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>21</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>206</v>
+        <v>249</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>222</v>
+        <v>218</v>
       </c>
     </row>
     <row r="4" spans="1:4" ht="30" customHeight="1">
       <c r="A4" s="1" t="s">
-        <v>160</v>
+        <v>248</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>22</v>
@@ -1302,21 +1308,21 @@
     </row>
     <row r="5" spans="1:4" ht="30" customHeight="1">
       <c r="A5" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>21</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>207</v>
+        <v>247</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>222</v>
+        <v>218</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="30" customHeight="1">
       <c r="A6" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>22</v>
@@ -1326,7 +1332,7 @@
     </row>
     <row r="7" spans="1:4" ht="30" customHeight="1">
       <c r="A7" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>22</v>
@@ -1336,21 +1342,21 @@
     </row>
     <row r="8" spans="1:4" ht="30" customHeight="1">
       <c r="A8" s="1" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>21</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>206</v>
+        <v>249</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>222</v>
+        <v>218</v>
       </c>
     </row>
     <row r="9" spans="1:4" ht="30" customHeight="1">
       <c r="A9" s="1" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>22</v>
@@ -1360,7 +1366,7 @@
     </row>
     <row r="10" spans="1:4" ht="30" customHeight="1">
       <c r="A10" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>22</v>
@@ -1370,7 +1376,7 @@
     </row>
     <row r="11" spans="1:4" ht="30" customHeight="1">
       <c r="A11" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>22</v>
@@ -1380,35 +1386,35 @@
     </row>
     <row r="12" spans="1:4" ht="30" customHeight="1">
       <c r="A12" s="1" t="s">
-        <v>36</v>
+        <v>246</v>
       </c>
       <c r="B12" s="1" t="s">
         <v>21</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>207</v>
+        <v>247</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>247</v>
+        <v>241</v>
       </c>
     </row>
     <row r="13" spans="1:4" ht="30" customHeight="1">
       <c r="A13" s="1" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="B13" s="1" t="s">
         <v>21</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>207</v>
+        <v>247</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>222</v>
+        <v>218</v>
       </c>
     </row>
     <row r="14" spans="1:4" ht="30" customHeight="1">
       <c r="A14" s="1" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="B14" s="1" t="s">
         <v>22</v>
@@ -1418,7 +1424,7 @@
     </row>
     <row r="15" spans="1:4" ht="30" customHeight="1">
       <c r="A15" s="1" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="B15" s="1" t="s">
         <v>22</v>
@@ -1428,21 +1434,21 @@
     </row>
     <row r="16" spans="1:4" ht="30" customHeight="1">
       <c r="A16" s="1" t="s">
-        <v>248</v>
+        <v>242</v>
       </c>
       <c r="B16" s="1" t="s">
         <v>21</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>223</v>
+        <v>219</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>222</v>
+        <v>218</v>
       </c>
     </row>
     <row r="17" spans="1:4" ht="30" customHeight="1">
       <c r="A17" s="1" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="B17" s="1" t="s">
         <v>22</v>
@@ -1452,7 +1458,7 @@
     </row>
     <row r="18" spans="1:4" ht="30" customHeight="1">
       <c r="A18" s="1" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B18" s="1" t="s">
         <v>22</v>
@@ -1462,7 +1468,7 @@
     </row>
     <row r="19" spans="1:4" ht="30" customHeight="1">
       <c r="A19" s="1" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="B19" s="1" t="s">
         <v>22</v>
@@ -1472,7 +1478,7 @@
     </row>
     <row r="20" spans="1:4" ht="30" customHeight="1">
       <c r="A20" s="1" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B20" s="1" t="s">
         <v>22</v>
@@ -1482,7 +1488,7 @@
     </row>
     <row r="21" spans="1:4" ht="30" customHeight="1">
       <c r="A21" s="1" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B21" s="1" t="s">
         <v>22</v>
@@ -1492,147 +1498,147 @@
     </row>
     <row r="22" spans="1:4" ht="30" customHeight="1">
       <c r="A22" s="1" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B22" s="1" t="s">
         <v>21</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>208</v>
+        <v>204</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>222</v>
+        <v>218</v>
       </c>
     </row>
     <row r="23" spans="1:4" ht="30" customHeight="1">
       <c r="A23" s="1" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B23" s="1" t="s">
         <v>21</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>222</v>
+        <v>218</v>
       </c>
     </row>
     <row r="24" spans="1:4" ht="30" customHeight="1">
       <c r="A24" s="1" t="s">
-        <v>224</v>
+        <v>220</v>
       </c>
       <c r="B24" s="1" t="s">
         <v>21</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>225</v>
+        <v>221</v>
       </c>
     </row>
     <row r="25" spans="1:4" ht="30" customHeight="1">
       <c r="A25" s="1" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B25" s="1" t="s">
         <v>21</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>225</v>
+        <v>221</v>
       </c>
     </row>
     <row r="26" spans="1:4" ht="30" customHeight="1">
       <c r="A26" s="1" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="B26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>225</v>
+        <v>221</v>
       </c>
     </row>
     <row r="27" spans="1:4" ht="30" customHeight="1">
       <c r="A27" s="1" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="B27" s="1" t="s">
         <v>21</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>225</v>
+        <v>221</v>
       </c>
     </row>
     <row r="28" spans="1:4" ht="30" customHeight="1">
       <c r="A28" s="1" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="B28" s="1" t="s">
         <v>21</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>225</v>
+        <v>221</v>
       </c>
     </row>
     <row r="29" spans="1:4" ht="30" customHeight="1">
       <c r="A29" s="1" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="B29" s="1" t="s">
         <v>21</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>225</v>
+        <v>221</v>
       </c>
     </row>
     <row r="30" spans="1:4" ht="30" customHeight="1">
       <c r="A30" s="1" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="B30" s="1" t="s">
         <v>21</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>222</v>
+        <v>218</v>
       </c>
     </row>
     <row r="31" spans="1:4" ht="30" customHeight="1">
       <c r="A31" s="1" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="B31" s="1" t="s">
         <v>21</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>222</v>
+        <v>218</v>
       </c>
     </row>
     <row r="32" spans="1:4" ht="30" customHeight="1">
       <c r="A32" s="1" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="B32" s="1" t="s">
         <v>22</v>
@@ -1642,7 +1648,7 @@
     </row>
     <row r="33" spans="1:4" ht="30" customHeight="1">
       <c r="A33" s="1" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="B33" s="1" t="s">
         <v>22</v>
@@ -1652,7 +1658,7 @@
     </row>
     <row r="34" spans="1:4" ht="30" customHeight="1">
       <c r="A34" s="1" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="B34" s="1" t="s">
         <v>22</v>
@@ -1662,7 +1668,7 @@
     </row>
     <row r="35" spans="1:4" ht="30" customHeight="1">
       <c r="A35" s="1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="B35" s="1" t="s">
         <v>22</v>
@@ -1672,7 +1678,7 @@
     </row>
     <row r="36" spans="1:4" ht="30" customHeight="1">
       <c r="A36" s="1" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="B36" s="1" t="s">
         <v>22</v>
@@ -1682,7 +1688,7 @@
     </row>
     <row r="37" spans="1:4" ht="30" customHeight="1">
       <c r="A37" s="1" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="B37" s="1" t="s">
         <v>22</v>
@@ -1692,7 +1698,7 @@
     </row>
     <row r="38" spans="1:4" ht="30" customHeight="1">
       <c r="A38" s="1" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="B38" s="1" t="s">
         <v>22</v>
@@ -1702,7 +1708,7 @@
     </row>
     <row r="39" spans="1:4" ht="30" customHeight="1">
       <c r="A39" s="1" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="B39" s="1" t="s">
         <v>22</v>
@@ -1712,7 +1718,7 @@
     </row>
     <row r="40" spans="1:4" ht="30" customHeight="1">
       <c r="A40" s="1" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="B40" s="1" t="s">
         <v>22</v>
@@ -1722,49 +1728,49 @@
     </row>
     <row r="41" spans="1:4" ht="30" customHeight="1">
       <c r="A41" s="1" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="B41" s="1" t="s">
         <v>21</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>209</v>
+        <v>205</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>222</v>
+        <v>218</v>
       </c>
     </row>
     <row r="42" spans="1:4" ht="30" customHeight="1">
       <c r="A42" s="1" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="B42" s="1" t="s">
         <v>21</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>222</v>
+        <v>218</v>
       </c>
     </row>
     <row r="43" spans="1:4" ht="30" customHeight="1">
       <c r="A43" s="1" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="B43" s="1" t="s">
         <v>21</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>210</v>
+        <v>206</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>222</v>
+        <v>218</v>
       </c>
     </row>
     <row r="44" spans="1:4" ht="30" customHeight="1">
       <c r="A44" s="1" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="B44" s="1" t="s">
         <v>22</v>
@@ -1774,7 +1780,7 @@
     </row>
     <row r="45" spans="1:4" ht="30" customHeight="1">
       <c r="A45" s="1" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="B45" s="1" t="s">
         <v>22</v>
@@ -1784,7 +1790,7 @@
     </row>
     <row r="46" spans="1:4" ht="30" customHeight="1">
       <c r="A46" s="1" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="B46" s="1" t="s">
         <v>22</v>
@@ -1794,7 +1800,7 @@
     </row>
     <row r="47" spans="1:4" ht="30" customHeight="1">
       <c r="A47" s="1" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="B47" s="1" t="s">
         <v>22</v>
@@ -1804,7 +1810,7 @@
     </row>
     <row r="48" spans="1:4" ht="30" customHeight="1">
       <c r="A48" s="1" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="B48" s="1" t="s">
         <v>22</v>
@@ -1814,7 +1820,7 @@
     </row>
     <row r="49" spans="1:4" ht="30" customHeight="1">
       <c r="A49" s="1" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="B49" s="1" t="s">
         <v>22</v>
@@ -1824,7 +1830,7 @@
     </row>
     <row r="50" spans="1:4" ht="30" customHeight="1">
       <c r="A50" s="1" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="B50" s="1" t="s">
         <v>22</v>
@@ -1834,7 +1840,7 @@
     </row>
     <row r="51" spans="1:4" ht="30" customHeight="1">
       <c r="A51" s="1" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="B51" s="1" t="s">
         <v>22</v>
@@ -1844,7 +1850,7 @@
     </row>
     <row r="52" spans="1:4" ht="30" customHeight="1">
       <c r="A52" s="1" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="B52" s="1" t="s">
         <v>22</v>
@@ -1854,7 +1860,7 @@
     </row>
     <row r="53" spans="1:4" ht="30" customHeight="1">
       <c r="A53" s="1" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="B53" s="1" t="s">
         <v>22</v>
@@ -1864,7 +1870,7 @@
     </row>
     <row r="54" spans="1:4" ht="30" customHeight="1">
       <c r="A54" s="1" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="B54" s="1" t="s">
         <v>22</v>
@@ -1874,7 +1880,7 @@
     </row>
     <row r="55" spans="1:4" ht="30" customHeight="1">
       <c r="A55" s="1" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="B55" s="1" t="s">
         <v>22</v>
@@ -1884,7 +1890,7 @@
     </row>
     <row r="56" spans="1:4" ht="30" customHeight="1">
       <c r="A56" s="1" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="B56" s="1" t="s">
         <v>22</v>
@@ -1894,7 +1900,7 @@
     </row>
     <row r="57" spans="1:4" ht="30" customHeight="1">
       <c r="A57" s="1" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="B57" s="1" t="s">
         <v>22</v>
@@ -1904,7 +1910,7 @@
     </row>
     <row r="58" spans="1:4" ht="30" customHeight="1">
       <c r="A58" s="1" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="B58" s="1" t="s">
         <v>22</v>
@@ -1914,7 +1920,7 @@
     </row>
     <row r="59" spans="1:4" ht="30" customHeight="1">
       <c r="A59" s="1" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="B59" s="1" t="s">
         <v>22</v>
@@ -1924,7 +1930,7 @@
     </row>
     <row r="60" spans="1:4" ht="30" customHeight="1">
       <c r="A60" s="1" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="B60" s="1" t="s">
         <v>22</v>
@@ -1934,7 +1940,7 @@
     </row>
     <row r="61" spans="1:4" ht="30" customHeight="1">
       <c r="A61" s="1" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="B61" s="1" t="s">
         <v>22</v>
@@ -1944,7 +1950,7 @@
     </row>
     <row r="62" spans="1:4" ht="30" customHeight="1">
       <c r="A62" s="1" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="B62" s="1" t="s">
         <v>22</v>
@@ -1954,7 +1960,7 @@
     </row>
     <row r="63" spans="1:4" ht="30" customHeight="1">
       <c r="A63" s="1" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="B63" s="1" t="s">
         <v>22</v>
@@ -1964,7 +1970,7 @@
     </row>
     <row r="64" spans="1:4" ht="30" customHeight="1">
       <c r="A64" s="1" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="B64" s="1" t="s">
         <v>22</v>
@@ -1974,63 +1980,63 @@
     </row>
     <row r="65" spans="1:4" ht="30" customHeight="1">
       <c r="A65" s="1" t="s">
-        <v>249</v>
+        <v>243</v>
       </c>
       <c r="B65" s="1" t="s">
         <v>21</v>
       </c>
       <c r="C65" s="1" t="s">
-        <v>211</v>
+        <v>207</v>
       </c>
       <c r="D65" s="1" t="s">
-        <v>222</v>
+        <v>218</v>
       </c>
     </row>
     <row r="66" spans="1:4" ht="30" customHeight="1">
       <c r="A66" s="1" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="B66" s="1" t="s">
         <v>21</v>
       </c>
       <c r="C66" s="1" t="s">
-        <v>211</v>
+        <v>207</v>
       </c>
       <c r="D66" s="1" t="s">
-        <v>222</v>
+        <v>218</v>
       </c>
     </row>
     <row r="67" spans="1:4" ht="30" customHeight="1">
       <c r="A67" s="1" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="B67" s="1" t="s">
         <v>21</v>
       </c>
       <c r="C67" s="1" t="s">
-        <v>211</v>
+        <v>207</v>
       </c>
       <c r="D67" s="1" t="s">
-        <v>222</v>
+        <v>218</v>
       </c>
     </row>
     <row r="68" spans="1:4" ht="30" customHeight="1">
       <c r="A68" s="1" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="B68" s="1" t="s">
         <v>21</v>
       </c>
       <c r="C68" s="1" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="D68" s="1" t="s">
-        <v>225</v>
+        <v>221</v>
       </c>
     </row>
     <row r="69" spans="1:4" ht="30" customHeight="1">
       <c r="A69" s="1" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="B69" s="1" t="s">
         <v>22</v>
@@ -2040,7 +2046,7 @@
     </row>
     <row r="70" spans="1:4" ht="30" customHeight="1">
       <c r="A70" s="1" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="B70" s="1" t="s">
         <v>22</v>
@@ -2050,7 +2056,7 @@
     </row>
     <row r="71" spans="1:4" ht="30" customHeight="1">
       <c r="A71" s="1" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="B71" s="1" t="s">
         <v>22</v>
@@ -2060,7 +2066,7 @@
     </row>
     <row r="72" spans="1:4" ht="30" customHeight="1">
       <c r="A72" s="1" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="B72" s="1" t="s">
         <v>22</v>
@@ -2070,7 +2076,7 @@
     </row>
     <row r="73" spans="1:4" ht="30" customHeight="1">
       <c r="A73" s="1" t="s">
-        <v>204</v>
+        <v>200</v>
       </c>
       <c r="B73" s="1" t="s">
         <v>22</v>
@@ -2080,7 +2086,7 @@
     </row>
     <row r="74" spans="1:4" ht="30" customHeight="1">
       <c r="A74" s="1" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="B74" s="1" t="s">
         <v>22</v>
@@ -2090,7 +2096,7 @@
     </row>
     <row r="75" spans="1:4" ht="30" customHeight="1">
       <c r="A75" s="1" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="B75" s="1" t="s">
         <v>22</v>
@@ -2100,7 +2106,7 @@
     </row>
     <row r="76" spans="1:4" ht="30" customHeight="1">
       <c r="A76" s="1" t="s">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="B76" s="1" t="s">
         <v>22</v>
@@ -2110,7 +2116,7 @@
     </row>
     <row r="77" spans="1:4" ht="30" customHeight="1">
       <c r="A77" s="1" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="B77" s="1" t="s">
         <v>22</v>
@@ -2120,7 +2126,7 @@
     </row>
     <row r="78" spans="1:4" ht="30" customHeight="1">
       <c r="A78" s="1" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="B78" s="1" t="s">
         <v>22</v>
@@ -2130,21 +2136,21 @@
     </row>
     <row r="79" spans="1:4" ht="30" customHeight="1">
       <c r="A79" s="1" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="B79" s="1" t="s">
         <v>21</v>
       </c>
       <c r="C79" s="1" t="s">
-        <v>212</v>
+        <v>208</v>
       </c>
       <c r="D79" s="1" t="s">
-        <v>222</v>
+        <v>218</v>
       </c>
     </row>
     <row r="80" spans="1:4" ht="30" customHeight="1">
       <c r="A80" s="1" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="B80" s="1" t="s">
         <v>22</v>
@@ -2154,7 +2160,7 @@
     </row>
     <row r="81" spans="1:4" ht="30" customHeight="1">
       <c r="A81" s="1" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="B81" s="1" t="s">
         <v>22</v>
@@ -2164,7 +2170,7 @@
     </row>
     <row r="82" spans="1:4" ht="30" customHeight="1">
       <c r="A82" s="1" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="B82" s="1" t="s">
         <v>22</v>
@@ -2174,7 +2180,7 @@
     </row>
     <row r="83" spans="1:4" ht="30" customHeight="1">
       <c r="A83" s="1" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="B83" s="1" t="s">
         <v>22</v>
@@ -2184,7 +2190,7 @@
     </row>
     <row r="84" spans="1:4" ht="30" customHeight="1">
       <c r="A84" s="1" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="B84" s="1" t="s">
         <v>22</v>
@@ -2194,7 +2200,7 @@
     </row>
     <row r="85" spans="1:4" ht="30" customHeight="1">
       <c r="A85" s="1" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="B85" s="1" t="s">
         <v>22</v>
@@ -2204,7 +2210,7 @@
     </row>
     <row r="86" spans="1:4" ht="30" customHeight="1">
       <c r="A86" s="1" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="B86" s="1" t="s">
         <v>22</v>
@@ -2214,7 +2220,7 @@
     </row>
     <row r="87" spans="1:4" ht="30" customHeight="1">
       <c r="A87" s="1" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="B87" s="1" t="s">
         <v>22</v>
@@ -2224,7 +2230,7 @@
     </row>
     <row r="88" spans="1:4" ht="30" customHeight="1">
       <c r="A88" s="1" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="B88" s="1" t="s">
         <v>22</v>
@@ -2234,7 +2240,7 @@
     </row>
     <row r="89" spans="1:4" ht="30" customHeight="1">
       <c r="A89" s="1" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="B89" s="1" t="s">
         <v>22</v>
@@ -2244,7 +2250,7 @@
     </row>
     <row r="90" spans="1:4" ht="30" customHeight="1">
       <c r="A90" s="1" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="B90" s="1" t="s">
         <v>22</v>
@@ -2254,7 +2260,7 @@
     </row>
     <row r="91" spans="1:4" ht="30" customHeight="1">
       <c r="A91" s="1" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="B91" s="1" t="s">
         <v>22</v>
@@ -2264,7 +2270,7 @@
     </row>
     <row r="92" spans="1:4" ht="30" customHeight="1">
       <c r="A92" s="1" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="B92" s="1" t="s">
         <v>22</v>
@@ -2274,7 +2280,7 @@
     </row>
     <row r="93" spans="1:4" ht="30" customHeight="1">
       <c r="A93" s="1" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="B93" s="1" t="s">
         <v>22</v>
@@ -2284,7 +2290,7 @@
     </row>
     <row r="94" spans="1:4" ht="30" customHeight="1">
       <c r="A94" s="1" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="B94" s="1" t="s">
         <v>22</v>
@@ -2294,7 +2300,7 @@
     </row>
     <row r="95" spans="1:4" ht="30" customHeight="1">
       <c r="A95" s="1" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="B95" s="1" t="s">
         <v>22</v>
@@ -2304,21 +2310,21 @@
     </row>
     <row r="96" spans="1:4" ht="30" customHeight="1">
       <c r="A96" s="1" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="B96" s="1" t="s">
         <v>21</v>
       </c>
       <c r="C96" s="1" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="D96" s="1" t="s">
-        <v>222</v>
+        <v>218</v>
       </c>
     </row>
     <row r="97" spans="1:4" ht="30" customHeight="1">
       <c r="A97" s="1" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="B97" s="1" t="s">
         <v>22</v>
@@ -2328,21 +2334,21 @@
     </row>
     <row r="98" spans="1:4" ht="30" customHeight="1">
       <c r="A98" s="1" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="B98" s="1" t="s">
         <v>21</v>
       </c>
       <c r="C98" s="1" t="s">
-        <v>237</v>
+        <v>244</v>
       </c>
       <c r="D98" s="1" t="s">
-        <v>222</v>
+        <v>218</v>
       </c>
     </row>
     <row r="99" spans="1:4" ht="30" customHeight="1">
       <c r="A99" s="1" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="B99" s="1" t="s">
         <v>22</v>
@@ -2352,7 +2358,7 @@
     </row>
     <row r="100" spans="1:4" ht="30" customHeight="1">
       <c r="A100" s="1" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="B100" s="1" t="s">
         <v>22</v>
@@ -2362,7 +2368,7 @@
     </row>
     <row r="101" spans="1:4" ht="30" customHeight="1">
       <c r="A101" s="1" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="B101" s="1" t="s">
         <v>22</v>
@@ -2372,7 +2378,7 @@
     </row>
     <row r="102" spans="1:4" ht="30" customHeight="1">
       <c r="A102" s="1" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="B102" s="1" t="s">
         <v>22</v>
@@ -2382,7 +2388,7 @@
     </row>
     <row r="103" spans="1:4" ht="30" customHeight="1">
       <c r="A103" s="1" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="B103" s="1" t="s">
         <v>22</v>
@@ -2392,7 +2398,7 @@
     </row>
     <row r="104" spans="1:4" ht="30" customHeight="1">
       <c r="A104" s="1" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="B104" s="1" t="s">
         <v>22</v>
@@ -2402,7 +2408,7 @@
     </row>
     <row r="105" spans="1:4" ht="30" customHeight="1">
       <c r="A105" s="1" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="B105" s="1" t="s">
         <v>22</v>
@@ -2412,7 +2418,7 @@
     </row>
     <row r="106" spans="1:4" ht="30" customHeight="1">
       <c r="A106" s="1" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="B106" s="1" t="s">
         <v>22</v>
@@ -2422,7 +2428,7 @@
     </row>
     <row r="107" spans="1:4" ht="30" customHeight="1">
       <c r="A107" s="1" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="B107" s="1" t="s">
         <v>22</v>
@@ -2432,7 +2438,7 @@
     </row>
     <row r="108" spans="1:4" ht="30" customHeight="1">
       <c r="A108" s="1" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="B108" s="1" t="s">
         <v>22</v>
@@ -2442,7 +2448,7 @@
     </row>
     <row r="109" spans="1:4" ht="30" customHeight="1">
       <c r="A109" s="1" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="B109" s="1" t="s">
         <v>22</v>
@@ -2452,7 +2458,7 @@
     </row>
     <row r="110" spans="1:4" ht="30" customHeight="1">
       <c r="A110" s="1" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="B110" s="1" t="s">
         <v>22</v>
@@ -2462,7 +2468,7 @@
     </row>
     <row r="111" spans="1:4" ht="30" customHeight="1">
       <c r="A111" s="1" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="B111" s="1" t="s">
         <v>22</v>
@@ -2472,7 +2478,7 @@
     </row>
     <row r="112" spans="1:4" ht="30" customHeight="1">
       <c r="A112" s="1" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="B112" s="1" t="s">
         <v>22</v>
@@ -2482,7 +2488,7 @@
     </row>
     <row r="113" spans="1:4" ht="30" customHeight="1">
       <c r="A113" s="1" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="B113" s="1" t="s">
         <v>22</v>
@@ -2492,7 +2498,7 @@
     </row>
     <row r="114" spans="1:4" ht="30" customHeight="1">
       <c r="A114" s="1" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="B114" s="1" t="s">
         <v>22</v>
@@ -2502,7 +2508,7 @@
     </row>
     <row r="115" spans="1:4" ht="30" customHeight="1">
       <c r="A115" s="1" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="B115" s="1" t="s">
         <v>22</v>
@@ -2512,7 +2518,7 @@
     </row>
     <row r="116" spans="1:4" ht="30" customHeight="1">
       <c r="A116" s="1" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="B116" s="1" t="s">
         <v>22</v>
@@ -2522,7 +2528,7 @@
     </row>
     <row r="117" spans="1:4" ht="30" customHeight="1">
       <c r="A117" s="1" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="B117" s="1" t="s">
         <v>22</v>
@@ -2532,7 +2538,7 @@
     </row>
     <row r="118" spans="1:4" ht="30" customHeight="1">
       <c r="A118" s="1" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="B118" s="1" t="s">
         <v>22</v>
@@ -2542,7 +2548,7 @@
     </row>
     <row r="119" spans="1:4" ht="30" customHeight="1">
       <c r="A119" s="1" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="B119" s="1" t="s">
         <v>22</v>
@@ -2552,7 +2558,7 @@
     </row>
     <row r="120" spans="1:4" ht="30" customHeight="1">
       <c r="A120" s="1" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="B120" s="1" t="s">
         <v>22</v>
@@ -2562,7 +2568,7 @@
     </row>
     <row r="121" spans="1:4" ht="30" customHeight="1">
       <c r="A121" s="1" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="B121" s="1" t="s">
         <v>22</v>
@@ -2572,7 +2578,7 @@
     </row>
     <row r="122" spans="1:4" ht="30" customHeight="1">
       <c r="A122" s="1" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="B122" s="1" t="s">
         <v>22</v>
@@ -2582,7 +2588,7 @@
     </row>
     <row r="123" spans="1:4" ht="30" customHeight="1">
       <c r="A123" s="1" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="B123" s="1" t="s">
         <v>22</v>
@@ -2592,7 +2598,7 @@
     </row>
     <row r="124" spans="1:4" ht="30" customHeight="1">
       <c r="A124" s="1" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="B124" s="1" t="s">
         <v>22</v>
@@ -2602,7 +2608,7 @@
     </row>
     <row r="125" spans="1:4" ht="30" customHeight="1">
       <c r="A125" s="1" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="B125" s="1" t="s">
         <v>22</v>
@@ -2612,7 +2618,7 @@
     </row>
     <row r="126" spans="1:4" ht="30" customHeight="1">
       <c r="A126" s="1" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="B126" s="1" t="s">
         <v>22</v>
@@ -2622,7 +2628,7 @@
     </row>
     <row r="127" spans="1:4" ht="30" customHeight="1">
       <c r="A127" s="1" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="B127" s="1" t="s">
         <v>22</v>
@@ -2632,7 +2638,7 @@
     </row>
     <row r="128" spans="1:4" ht="30" customHeight="1">
       <c r="A128" s="1" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="B128" s="1" t="s">
         <v>22</v>
@@ -2642,91 +2648,91 @@
     </row>
     <row r="129" spans="1:4" ht="30" customHeight="1">
       <c r="A129" s="1" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="B129" s="1" t="s">
         <v>21</v>
       </c>
       <c r="C129" s="1" t="s">
-        <v>213</v>
+        <v>209</v>
       </c>
       <c r="D129" s="1" t="s">
-        <v>222</v>
+        <v>218</v>
       </c>
     </row>
     <row r="130" spans="1:4" ht="30" customHeight="1">
       <c r="A130" s="1" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="B130" s="1" t="s">
         <v>21</v>
       </c>
       <c r="C130" s="1" t="s">
-        <v>213</v>
+        <v>209</v>
       </c>
       <c r="D130" s="1" t="s">
-        <v>222</v>
+        <v>218</v>
       </c>
     </row>
     <row r="131" spans="1:4" ht="30" customHeight="1">
       <c r="A131" s="1" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="B131" s="1" t="s">
         <v>21</v>
       </c>
       <c r="C131" s="1" t="s">
-        <v>213</v>
+        <v>209</v>
       </c>
       <c r="D131" s="1" t="s">
-        <v>222</v>
+        <v>218</v>
       </c>
     </row>
     <row r="132" spans="1:4" ht="30" customHeight="1">
       <c r="A132" s="1" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="B132" s="1" t="s">
         <v>21</v>
       </c>
       <c r="C132" s="1" t="s">
-        <v>213</v>
+        <v>209</v>
       </c>
       <c r="D132" s="1" t="s">
-        <v>222</v>
+        <v>218</v>
       </c>
     </row>
     <row r="133" spans="1:4" ht="30" customHeight="1">
       <c r="A133" s="1" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="B133" s="1" t="s">
         <v>21</v>
       </c>
       <c r="C133" s="1" t="s">
-        <v>213</v>
+        <v>209</v>
       </c>
       <c r="D133" s="1" t="s">
-        <v>222</v>
+        <v>218</v>
       </c>
     </row>
     <row r="134" spans="1:4" ht="30" customHeight="1">
       <c r="A134" s="1" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="B134" s="1" t="s">
         <v>21</v>
       </c>
       <c r="C134" s="1" t="s">
-        <v>213</v>
+        <v>209</v>
       </c>
       <c r="D134" s="1" t="s">
-        <v>222</v>
+        <v>218</v>
       </c>
     </row>
     <row r="135" spans="1:4" ht="30" customHeight="1">
       <c r="A135" s="1" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="B135" s="1" t="s">
         <v>22</v>
@@ -2736,7 +2742,7 @@
     </row>
     <row r="136" spans="1:4" ht="30" customHeight="1">
       <c r="A136" s="1" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="B136" s="1" t="s">
         <v>22</v>
@@ -2746,147 +2752,147 @@
     </row>
     <row r="137" spans="1:4" ht="30" customHeight="1">
       <c r="A137" s="1" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="B137" s="1" t="s">
         <v>20</v>
       </c>
       <c r="C137" s="1" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="D137" s="1" t="s">
-        <v>222</v>
+        <v>218</v>
       </c>
     </row>
     <row r="138" spans="1:4" ht="30" customHeight="1">
       <c r="A138" s="1" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="B138" s="1" t="s">
         <v>20</v>
       </c>
       <c r="C138" s="1" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="D138" s="1" t="s">
-        <v>222</v>
+        <v>218</v>
       </c>
     </row>
     <row r="139" spans="1:4" ht="30" customHeight="1">
       <c r="A139" s="1" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="B139" s="1" t="s">
         <v>20</v>
       </c>
       <c r="C139" s="1" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="D139" s="1" t="s">
-        <v>222</v>
+        <v>218</v>
       </c>
     </row>
     <row r="140" spans="1:4" ht="30" customHeight="1">
       <c r="A140" s="1" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="B140" s="1" t="s">
         <v>20</v>
       </c>
       <c r="C140" s="1" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="D140" s="1" t="s">
-        <v>222</v>
+        <v>218</v>
       </c>
     </row>
     <row r="141" spans="1:4" ht="30" customHeight="1">
       <c r="A141" s="1" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="B141" s="1" t="s">
         <v>20</v>
       </c>
       <c r="C141" s="1" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="D141" s="1" t="s">
-        <v>222</v>
+        <v>218</v>
       </c>
     </row>
     <row r="142" spans="1:4" ht="30" customHeight="1">
       <c r="A142" s="1" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="B142" s="1" t="s">
         <v>20</v>
       </c>
       <c r="C142" s="1" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="D142" s="1" t="s">
-        <v>222</v>
+        <v>218</v>
       </c>
     </row>
     <row r="143" spans="1:4" ht="30" customHeight="1">
       <c r="A143" s="1" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="B143" s="1" t="s">
         <v>21</v>
       </c>
       <c r="C143" s="1" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="D143" s="1" t="s">
-        <v>222</v>
+        <v>218</v>
       </c>
     </row>
     <row r="144" spans="1:4" ht="30" customHeight="1">
       <c r="A144" s="1" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="B144" s="1" t="s">
         <v>21</v>
       </c>
       <c r="C144" s="1" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="D144" s="1" t="s">
-        <v>222</v>
+        <v>218</v>
       </c>
     </row>
     <row r="145" spans="1:4" ht="30" customHeight="1">
       <c r="A145" s="1" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="B145" s="1" t="s">
         <v>21</v>
       </c>
       <c r="C145" s="1" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="D145" s="1" t="s">
-        <v>222</v>
+        <v>218</v>
       </c>
     </row>
     <row r="146" spans="1:4" ht="30" customHeight="1">
       <c r="A146" s="1" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="B146" s="1" t="s">
         <v>21</v>
       </c>
       <c r="C146" s="1" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="D146" s="1" t="s">
-        <v>222</v>
+        <v>218</v>
       </c>
     </row>
     <row r="147" spans="1:4" ht="30" customHeight="1">
       <c r="A147" s="1" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="B147" s="1" t="s">
         <v>22</v>
@@ -2896,7 +2902,7 @@
     </row>
     <row r="148" spans="1:4" ht="30" customHeight="1">
       <c r="A148" s="1" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="B148" s="1" t="s">
         <v>22</v>
@@ -2906,7 +2912,7 @@
     </row>
     <row r="149" spans="1:4" ht="30" customHeight="1">
       <c r="A149" s="1" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="B149" s="1" t="s">
         <v>22</v>
@@ -2916,7 +2922,7 @@
     </row>
     <row r="150" spans="1:4" ht="30" customHeight="1">
       <c r="A150" s="1" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="B150" s="1" t="s">
         <v>22</v>
@@ -2926,35 +2932,35 @@
     </row>
     <row r="151" spans="1:4" ht="30" customHeight="1">
       <c r="A151" s="1" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="B151" s="1" t="s">
         <v>21</v>
       </c>
       <c r="C151" s="1" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="D151" s="1" t="s">
-        <v>222</v>
+        <v>218</v>
       </c>
     </row>
     <row r="152" spans="1:4" ht="30" customHeight="1">
       <c r="A152" s="1" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="B152" s="1" t="s">
         <v>21</v>
       </c>
       <c r="C152" s="1" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="D152" s="1" t="s">
-        <v>222</v>
+        <v>218</v>
       </c>
     </row>
     <row r="153" spans="1:4" ht="30" customHeight="1">
       <c r="A153" s="1" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="B153" s="1" t="s">
         <v>22</v>
@@ -2964,7 +2970,7 @@
     </row>
     <row r="154" spans="1:4" ht="30" customHeight="1">
       <c r="A154" s="1" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="B154" s="1" t="s">
         <v>22</v>
@@ -2974,7 +2980,7 @@
     </row>
     <row r="155" spans="1:4" ht="30" customHeight="1">
       <c r="A155" s="1" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="B155" s="1" t="s">
         <v>22</v>
@@ -2984,203 +2990,203 @@
     </row>
     <row r="156" spans="1:4" ht="30" customHeight="1">
       <c r="A156" s="1" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="B156" s="1" t="s">
         <v>21</v>
       </c>
       <c r="C156" s="1" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="D156" s="1" t="s">
-        <v>222</v>
+        <v>218</v>
       </c>
     </row>
     <row r="157" spans="1:4" ht="30" customHeight="1">
       <c r="A157" s="1" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="B157" s="1" t="s">
         <v>21</v>
       </c>
       <c r="C157" s="1" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="D157" s="1" t="s">
-        <v>222</v>
+        <v>218</v>
       </c>
     </row>
     <row r="158" spans="1:4" ht="30" customHeight="1">
       <c r="A158" s="1" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="B158" s="1" t="s">
         <v>21</v>
       </c>
       <c r="C158" s="1" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="D158" s="1" t="s">
-        <v>222</v>
+        <v>218</v>
       </c>
     </row>
     <row r="159" spans="1:4" ht="30" customHeight="1">
       <c r="A159" s="1" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="B159" s="1" t="s">
-        <v>227</v>
+        <v>223</v>
       </c>
       <c r="C159" s="1" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="D159" s="1" t="s">
-        <v>222</v>
+        <v>218</v>
       </c>
     </row>
     <row r="160" spans="1:4" ht="30" customHeight="1">
       <c r="A160" s="1" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="B160" s="1" t="s">
-        <v>227</v>
+        <v>223</v>
       </c>
       <c r="C160" s="1" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="D160" s="1" t="s">
-        <v>222</v>
+        <v>218</v>
       </c>
     </row>
     <row r="161" spans="1:4" ht="30" customHeight="1">
       <c r="A161" s="1" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="B161" s="1" t="s">
-        <v>227</v>
+        <v>223</v>
       </c>
       <c r="C161" s="1" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="D161" s="1" t="s">
-        <v>222</v>
+        <v>218</v>
       </c>
     </row>
     <row r="162" spans="1:4" ht="30" customHeight="1">
       <c r="A162" s="1" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="B162" s="1" t="s">
-        <v>227</v>
+        <v>223</v>
       </c>
       <c r="C162" s="1" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="D162" s="1" t="s">
-        <v>222</v>
+        <v>218</v>
       </c>
     </row>
     <row r="163" spans="1:4" ht="30" customHeight="1">
       <c r="A163" s="1" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="B163" s="1" t="s">
-        <v>227</v>
+        <v>223</v>
       </c>
       <c r="C163" s="1" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="D163" s="1" t="s">
-        <v>222</v>
+        <v>218</v>
       </c>
     </row>
     <row r="164" spans="1:4" ht="30" customHeight="1">
       <c r="A164" s="1" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="B164" s="1" t="s">
-        <v>227</v>
+        <v>223</v>
       </c>
       <c r="C164" s="1" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="D164" s="1" t="s">
-        <v>222</v>
+        <v>218</v>
       </c>
     </row>
     <row r="165" spans="1:4" ht="30" customHeight="1">
       <c r="A165" s="1" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="B165" s="1" t="s">
         <v>21</v>
       </c>
       <c r="C165" s="1" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="D165" s="1" t="s">
-        <v>222</v>
+        <v>218</v>
       </c>
     </row>
     <row r="166" spans="1:4" ht="30" customHeight="1">
       <c r="A166" s="1" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="B166" s="1" t="s">
         <v>21</v>
       </c>
       <c r="C166" s="1" t="s">
-        <v>214</v>
+        <v>210</v>
       </c>
       <c r="D166" s="1" t="s">
-        <v>222</v>
+        <v>218</v>
       </c>
     </row>
     <row r="167" spans="1:4" ht="30" customHeight="1">
       <c r="A167" s="1" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="B167" s="1" t="s">
         <v>21</v>
       </c>
       <c r="C167" s="1" t="s">
-        <v>215</v>
+        <v>211</v>
       </c>
       <c r="D167" s="1" t="s">
-        <v>226</v>
+        <v>222</v>
       </c>
     </row>
     <row r="168" spans="1:4" ht="30" customHeight="1">
       <c r="A168" s="1" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="B168" s="1" t="s">
         <v>21</v>
       </c>
       <c r="C168" s="1" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="D168" s="1" t="s">
-        <v>222</v>
+        <v>218</v>
       </c>
     </row>
     <row r="169" spans="1:4" ht="30" customHeight="1">
       <c r="A169" s="1" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="B169" s="1" t="s">
         <v>21</v>
       </c>
       <c r="C169" s="1" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="D169" s="1" t="s">
-        <v>222</v>
+        <v>218</v>
       </c>
     </row>
     <row r="170" spans="1:4" ht="30" customHeight="1">
       <c r="A170" s="1" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="B170" s="1" t="s">
         <v>22</v>
@@ -3190,21 +3196,21 @@
     </row>
     <row r="171" spans="1:4" ht="30" customHeight="1">
       <c r="A171" s="1" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="B171" s="1" t="s">
         <v>21</v>
       </c>
       <c r="C171" s="1" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="D171" s="1" t="s">
-        <v>222</v>
+        <v>218</v>
       </c>
     </row>
     <row r="172" spans="1:4" ht="30" customHeight="1">
       <c r="A172" s="1" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="B172" s="1" t="s">
         <v>22</v>
@@ -3214,35 +3220,35 @@
     </row>
     <row r="173" spans="1:4" ht="30" customHeight="1">
       <c r="A173" s="1" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="B173" s="1" t="s">
         <v>21</v>
       </c>
       <c r="C173" s="1" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="D173" s="1" t="s">
-        <v>222</v>
+        <v>218</v>
       </c>
     </row>
     <row r="174" spans="1:4" ht="30" customHeight="1">
       <c r="A174" s="1" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="B174" s="1" t="s">
         <v>21</v>
       </c>
       <c r="C174" s="1" t="s">
-        <v>216</v>
+        <v>212</v>
       </c>
       <c r="D174" s="1" t="s">
-        <v>222</v>
+        <v>218</v>
       </c>
     </row>
     <row r="175" spans="1:4" ht="30" customHeight="1">
       <c r="A175" s="1" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="B175" s="1" t="s">
         <v>22</v>
@@ -3252,7 +3258,7 @@
     </row>
     <row r="176" spans="1:4" ht="30" customHeight="1">
       <c r="A176" s="1" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="B176" s="1" t="s">
         <v>22</v>
@@ -3262,21 +3268,21 @@
     </row>
     <row r="177" spans="1:4" ht="30" customHeight="1">
       <c r="A177" s="1" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="B177" s="1" t="s">
         <v>21</v>
       </c>
       <c r="C177" s="1" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="D177" s="1" t="s">
-        <v>222</v>
+        <v>218</v>
       </c>
     </row>
     <row r="178" spans="1:4" ht="30" customHeight="1">
       <c r="A178" s="1" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="B178" s="1" t="s">
         <v>22</v>
@@ -3286,7 +3292,7 @@
     </row>
     <row r="179" spans="1:4" ht="30" customHeight="1">
       <c r="A179" s="1" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="B179" s="1" t="s">
         <v>22</v>
@@ -3323,10 +3329,10 @@
         <v>19</v>
       </c>
       <c r="C1" s="1" t="s">
+        <v>213</v>
+      </c>
+      <c r="D1" s="2" t="s">
         <v>217</v>
-      </c>
-      <c r="D1" s="2" t="s">
-        <v>221</v>
       </c>
     </row>
     <row r="2" spans="1:4" ht="20.100000000000001" customHeight="1">
@@ -3337,10 +3343,10 @@
         <v>21</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>220</v>
+        <v>216</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>222</v>
+        <v>218</v>
       </c>
     </row>
     <row r="3" spans="1:4" hidden="1">
@@ -3359,10 +3365,10 @@
         <v>21</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>218</v>
+        <v>214</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>222</v>
+        <v>218</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="20.100000000000001" customHeight="1">
@@ -3373,10 +3379,10 @@
         <v>21</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>219</v>
+        <v>215</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>222</v>
+        <v>218</v>
       </c>
     </row>
     <row r="6" spans="1:4" hidden="1">
@@ -3395,10 +3401,10 @@
         <v>21</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>220</v>
+        <v>216</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>222</v>
+        <v>218</v>
       </c>
     </row>
   </sheetData>
@@ -3464,7 +3470,6 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <sheetPr filterMode="1"/>
   <dimension ref="A1:D15"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
@@ -3485,7 +3490,7 @@
         <v>17</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>229</v>
+        <v>225</v>
       </c>
     </row>
     <row r="2" spans="1:4" ht="20.100000000000001" customHeight="1">
@@ -3493,109 +3498,109 @@
         <v>7</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>227</v>
+        <v>223</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" ht="20.100000000000001" hidden="1" customHeight="1">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" ht="20.100000000000001" customHeight="1">
       <c r="A3" s="1" t="s">
         <v>8</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="4" t="s">
-        <v>230</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" ht="20.100000000000001" hidden="1" customHeight="1">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" ht="20.100000000000001" customHeight="1">
       <c r="A4" s="1" t="s">
         <v>9</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="C4" s="1"/>
       <c r="D4" s="4" t="s">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" ht="20.100000000000001" hidden="1" customHeight="1">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" ht="20.100000000000001" customHeight="1">
       <c r="A5" s="1" t="s">
         <v>10</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="C5" s="1"/>
       <c r="D5" s="4" t="s">
-        <v>233</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" ht="20.100000000000001" hidden="1" customHeight="1">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" ht="20.100000000000001" customHeight="1">
       <c r="A6" s="1" t="s">
         <v>11</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="C6" s="1"/>
       <c r="D6" s="4" t="s">
-        <v>234</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" ht="36.75" hidden="1" customHeight="1">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" ht="36.75" customHeight="1">
       <c r="A7" s="1" t="s">
-        <v>235</v>
+        <v>231</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
       <c r="C7" s="1"/>
       <c r="D7" s="4" t="s">
-        <v>236</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" ht="20.100000000000001" hidden="1" customHeight="1">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" ht="20.100000000000001" customHeight="1">
       <c r="A8" s="1" t="s">
         <v>12</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
       <c r="C8" s="1"/>
       <c r="D8" s="4" t="s">
-        <v>238</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" ht="20.100000000000001" hidden="1" customHeight="1">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" ht="20.100000000000001" customHeight="1">
       <c r="A9" s="1" t="s">
         <v>13</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
       <c r="C9" s="1"/>
       <c r="D9" s="4" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" ht="26.25" hidden="1" customHeight="1">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" ht="26.25" customHeight="1">
       <c r="A10" s="1" t="s">
-        <v>240</v>
+        <v>235</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
       <c r="C10" s="1"/>
       <c r="D10" s="4" t="s">
-        <v>241</v>
+        <v>236</v>
       </c>
     </row>
     <row r="11" spans="1:4" ht="20.100000000000001" customHeight="1">
@@ -3603,49 +3608,49 @@
         <v>14</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>242</v>
+        <v>237</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" ht="20.100000000000001" hidden="1" customHeight="1">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" ht="20.100000000000001" customHeight="1">
       <c r="A12" s="1" t="s">
         <v>15</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
       <c r="C12" s="1"/>
       <c r="D12" s="4" t="s">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4" ht="20.100000000000001" hidden="1" customHeight="1">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" ht="20.100000000000001" customHeight="1">
       <c r="A13" s="1" t="s">
-        <v>244</v>
+        <v>238</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
       <c r="C13" s="1"/>
       <c r="D13" s="4" t="s">
-        <v>245</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4" ht="20.100000000000001" hidden="1" customHeight="1">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" ht="20.100000000000001" customHeight="1">
       <c r="A14" s="1" t="s">
         <v>16</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
       <c r="C14" s="1"/>
       <c r="D14" s="4" t="s">
-        <v>246</v>
+        <v>240</v>
       </c>
     </row>
     <row r="15" spans="1:4" ht="20.100000000000001" customHeight="1">
@@ -3653,22 +3658,18 @@
         <v>29</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>242</v>
+        <v>237</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
       <c r="D15" s="4" t="s">
-        <v>222</v>
+        <v>218</v>
       </c>
     </row>
   </sheetData>
   <autoFilter ref="B1:B15">
-    <filterColumn colId="0">
-      <filters>
-        <filter val="是"/>
-      </filters>
-    </filterColumn>
+    <filterColumn colId="0"/>
   </autoFilter>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
